--- a/siglip_out_female.xlsx
+++ b/siglip_out_female.xlsx
@@ -1,40 +1,267 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
+  <si>
+    <t>Trait</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Modified\woman1\woman1_heavy_build.png</t>
+  </si>
+  <si>
+    <t>Modified\woman1\woman1_muscular.png</t>
+  </si>
+  <si>
+    <t>Modified\woman1\woman1_no_makeup.png</t>
+  </si>
+  <si>
+    <t>Modified\woman1\woman1_short_hair.png</t>
+  </si>
+  <si>
+    <t>Modified\woman1\woman1_tall.png</t>
+  </si>
+  <si>
+    <t>Modified\woman2\woman2_heavy_build.png</t>
+  </si>
+  <si>
+    <t>Modified\woman2\woman2_muscular.png</t>
+  </si>
+  <si>
+    <t>Modified\woman2\woman2_no_makeup.png</t>
+  </si>
+  <si>
+    <t>Modified\woman2\woman2_short_hair.png</t>
+  </si>
+  <si>
+    <t>Modified\woman2\woman2_tall.png</t>
+  </si>
+  <si>
+    <t>Modified\woman3\woman3_heavy_build.png</t>
+  </si>
+  <si>
+    <t>Modified\woman3\woman3_muscular.png</t>
+  </si>
+  <si>
+    <t>Modified\woman3\woman3_no_makeup.png</t>
+  </si>
+  <si>
+    <t>Modified\woman3\woman3_short_hair.png</t>
+  </si>
+  <si>
+    <t>Modified\woman3\woman3_tall.png</t>
+  </si>
+  <si>
+    <t>woman1_original.jpg</t>
+  </si>
+  <si>
+    <t>woman2_original.png</t>
+  </si>
+  <si>
+    <t>woman3_original.jpg</t>
+  </si>
+  <si>
+    <t>woman4_original.jpg</t>
+  </si>
+  <si>
+    <t>woman5_original.jpg</t>
+  </si>
+  <si>
+    <t>is talkative</t>
+  </si>
+  <si>
+    <t>Extraversion</t>
+  </si>
+  <si>
+    <t>is reserved</t>
+  </si>
+  <si>
+    <t>is full of energy</t>
+  </si>
+  <si>
+    <t>generates a lot of enthusiasm</t>
+  </si>
+  <si>
+    <t>tends to be quiet</t>
+  </si>
+  <si>
+    <t>has an assertive personality</t>
+  </si>
+  <si>
+    <t>is sometimes shy, inhibited</t>
+  </si>
+  <si>
+    <t>is outgoing, sociable</t>
+  </si>
+  <si>
+    <t>tends to find fault with others</t>
+  </si>
+  <si>
+    <t>Agreeableness</t>
+  </si>
+  <si>
+    <t>is helpful and unselfish with others</t>
+  </si>
+  <si>
+    <t>starts quarrels with others</t>
+  </si>
+  <si>
+    <t>has a forgiving nature</t>
+  </si>
+  <si>
+    <t>is generally trusting</t>
+  </si>
+  <si>
+    <t>can be cold and aloof</t>
+  </si>
+  <si>
+    <t>is considerate and kind to almost everyone</t>
+  </si>
+  <si>
+    <t>is sometimes rude to others</t>
+  </si>
+  <si>
+    <t>likes to cooperate with others</t>
+  </si>
+  <si>
+    <t>does a thorough job</t>
+  </si>
+  <si>
+    <t>Conscientiousness</t>
+  </si>
+  <si>
+    <t>can be somewhat careless</t>
+  </si>
+  <si>
+    <t>is a reliable worker</t>
+  </si>
+  <si>
+    <t>tends to be disorganized</t>
+  </si>
+  <si>
+    <t>tends to be lazy</t>
+  </si>
+  <si>
+    <t>perseveres until the task is finished</t>
+  </si>
+  <si>
+    <t>does things efficiently</t>
+  </si>
+  <si>
+    <t>makes plans and follows through with them</t>
+  </si>
+  <si>
+    <t>is easily distracted</t>
+  </si>
+  <si>
+    <t>is depressed, blue</t>
+  </si>
+  <si>
+    <t>Neuroticism</t>
+  </si>
+  <si>
+    <t>is relaxed, handles stress well</t>
+  </si>
+  <si>
+    <t>can be tense</t>
+  </si>
+  <si>
+    <t>worries a lot</t>
+  </si>
+  <si>
+    <t>is emotionally stable, not easily upset</t>
+  </si>
+  <si>
+    <t>can be moody</t>
+  </si>
+  <si>
+    <t>remains calm in tense situations</t>
+  </si>
+  <si>
+    <t>gets nervous easily</t>
+  </si>
+  <si>
+    <t>is original, comes up with new ideas</t>
+  </si>
+  <si>
+    <t>Openness</t>
+  </si>
+  <si>
+    <t>is curious about many different things</t>
+  </si>
+  <si>
+    <t>is ingenious, a deep thinker</t>
+  </si>
+  <si>
+    <t>has an active imagination</t>
+  </si>
+  <si>
+    <t>is inventive</t>
+  </si>
+  <si>
+    <t>values artistic, aesthetic experiences</t>
+  </si>
+  <si>
+    <t>prefers work that is routine</t>
+  </si>
+  <si>
+    <t>likes to reflect, play with ideas</t>
+  </si>
+  <si>
+    <t>is sophisticated in art, music, or literature</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -46,81 +273,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -129,10 +309,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -170,69 +350,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -256,54 +438,53 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -313,7 +494,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -322,7 +503,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -331,7 +512,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -339,10 +520,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -371,7 +552,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -384,13 +565,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -408,3223 +588,3030 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:V44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Trait</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Modified\woman1\woman1_heavy_build.png</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Modified\woman1\woman1_muscular.png</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Modified\woman1\woman1_no_makeup.png</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Modified\woman1\woman1_short_hair.png</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Modified\woman1\woman1_tall.png</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Modified\woman2\woman2_heavy_build.png</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Modified\woman2\woman2_muscular.png</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Modified\woman2\woman2_no_makeup.png</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Modified\woman2\woman2_short_hair.png</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Modified\woman2\woman2_tall.png</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Modified\woman3\woman3_heavy_build.png</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Modified\woman3\woman3_muscular.png</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Modified\woman3\woman3_no_makeup.png</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Modified\woman3\woman3_short_hair.png</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Modified\woman3\woman3_tall.png</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>woman1_original.jpg</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>woman2_original.png</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>woman3_original.jpg</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>woman4_original.jpg</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>woman5_original.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>is talkative</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3">
         <v>0.04819560050964355</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3">
         <v>0.05369172245264053</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3">
         <v>0.05409809201955795</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3">
         <v>0.05920938402414322</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3">
         <v>0.05399888753890991</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3">
         <v>0.05065952986478806</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3">
         <v>0.03541335836052895</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3">
         <v>0.05356951430439949</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3">
         <v>0.05267328768968582</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3">
         <v>0.05498738959431648</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="3">
         <v>0.04990476369857788</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3">
         <v>0.04740092530846596</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3">
         <v>0.06108781695365906</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="3">
         <v>0.0534418597817421</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="3">
         <v>0.06043826416134834</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="3">
         <v>0.05663044005632401</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="3">
         <v>0.05659561976790428</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="3">
         <v>0.05560531839728355</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="3">
         <v>0.05932139232754707</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" s="3">
         <v>0.06234120577573776</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>is reserved</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3">
         <v>0.03479139506816864</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3">
         <v>0.04033245146274567</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3">
         <v>0.04519659280776978</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3">
         <v>0.04558618739247322</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3">
         <v>0.04598721489310265</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3">
         <v>0.02467936836183071</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3">
         <v>0.02066670544445515</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3">
         <v>0.03479605168104172</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3">
         <v>0.03543921560049057</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3">
         <v>0.03599001094698906</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="3">
         <v>0.02786770462989807</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3">
         <v>0.03321496024727821</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3">
         <v>0.03763607889413834</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="3">
         <v>0.03397868573665619</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="3">
         <v>0.03543085604906082</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="3">
         <v>0.04314904287457466</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="3">
         <v>0.03326652944087982</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="3">
         <v>0.02961819060146809</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="3">
         <v>0.0338367186486721</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" s="3">
         <v>0.03251093626022339</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>is full of energy</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3">
         <v>0.05954457074403763</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3">
         <v>0.06433945149183273</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3">
         <v>0.06205608323216438</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3">
         <v>0.0643591433763504</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.06638201326131821</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="G4" s="3">
+        <v>0.0663820132613182</v>
+      </c>
+      <c r="H4" s="3">
         <v>0.06086836010217667</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3">
         <v>0.05980235710740089</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3">
         <v>0.06305673718452454</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3">
         <v>0.06502263993024826</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3">
         <v>0.06575382500886917</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3">
         <v>0.05604685097932816</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3">
         <v>0.05593011528253555</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3">
         <v>0.05680631846189499</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="3">
         <v>0.05591408908367157</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="3">
         <v>0.05968478322029114</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="3">
         <v>0.0649278312921524</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="3">
         <v>0.0681326761841774</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="3">
         <v>0.0540229007601738</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="3">
         <v>0.06899449229240417</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" s="3">
         <v>0.06295031309127808</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>generates a lot of enthusiasm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3">
         <v>0.06751636415719986</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3">
         <v>0.0734020471572876</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3">
         <v>0.06425641477108002</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3">
         <v>0.07239747047424316</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3">
         <v>0.06476804614067078</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3">
         <v>0.06859973818063736</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3">
         <v>0.06489364057779312</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="3">
         <v>0.07607856392860413</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3">
         <v>0.07952865213155746</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3">
         <v>0.07965924590826035</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="3">
         <v>0.06982139497995377</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3">
         <v>0.0720936506986618</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3">
         <v>0.07292982935905457</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="3">
         <v>0.06411031633615494</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3">
         <v>0.07580254971981049</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="3">
         <v>0.07193566113710403</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="3">
         <v>0.08319035172462463</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="3">
         <v>0.06679568439722061</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5" s="3">
         <v>0.0729338526725769</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" s="3">
         <v>0.08092527836561203</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tends to be quiet</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3">
         <v>0.01420033350586891</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3">
         <v>0.02812691777944565</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3">
         <v>0.02156144566833973</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3">
         <v>0.02258316986262798</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3">
         <v>0.02511370182037354</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3">
         <v>0.01048105210065842</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3">
         <v>0.02770016901195049</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="3">
         <v>0.01996172219514847</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3">
         <v>0.02169737964868546</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3">
         <v>0.02344574779272079</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3">
         <v>0.01802794449031353</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3">
         <v>0.02598590962588787</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3">
         <v>0.02476801350712776</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="3">
         <v>0.02367888949811459</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="3">
         <v>0.02756121568381786</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="3">
         <v>0.0231388732790947</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="3">
         <v>0.02089239656925201</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6" s="3">
         <v>0.02248717099428177</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6" s="3">
         <v>0.02774855121970177</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" s="3">
         <v>0.03569304943084717</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>has an assertive personality</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="3">
         <v>0.08337989449501038</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3">
         <v>0.08247369527816772</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3">
         <v>0.08287862688302994</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3">
         <v>0.08650974184274673</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3">
         <v>0.0817936509847641</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3">
         <v>0.06720809638500214</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3">
         <v>0.05112197622656822</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3">
         <v>0.07861657440662384</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3">
         <v>0.08327347040176392</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3">
         <v>0.07554458826780319</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="3">
         <v>0.08451878279447556</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3">
         <v>0.07777140289545059</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3">
         <v>0.08891043066978455</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="3">
         <v>0.08953049033880234</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="3">
         <v>0.08629905432462692</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" s="3">
         <v>0.0851573646068573</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="3">
         <v>0.08062366396188736</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="3">
         <v>0.08195805549621582</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7" s="3">
         <v>0.07549872249364853</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" s="3">
         <v>0.07724808901548386</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>is sometimes shy, inhibited</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3">
         <v>0.07976994663476944</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3">
         <v>0.09327749907970428</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3">
         <v>0.08455102890729904</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3">
         <v>0.08995547145605087</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3">
         <v>0.08181437104940414</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3">
         <v>0.06108132377266884</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3">
         <v>0.06955923140048981</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="3">
         <v>0.06871117651462555</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3">
         <v>0.06785769015550613</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3">
         <v>0.07060565799474716</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3">
         <v>0.06164061278104782</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3">
         <v>0.06781958788633347</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3">
         <v>0.06714211404323578</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="3">
         <v>0.05917524546384811</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="3">
         <v>0.06806494295597076</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8" s="3">
         <v>0.09078509360551834</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="3">
         <v>0.06897357106208801</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" s="3">
         <v>0.06557249277830124</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8" s="3">
         <v>0.0731942430138588</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8" s="3">
         <v>0.07428449392318726</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>is outgoing, sociable</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Extraversion</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3">
         <v>0.05308482423424721</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3">
         <v>0.066020667552948</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3">
         <v>0.06564678996801376</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3">
         <v>0.06083356589078903</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3">
         <v>0.06143420189619064</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3">
         <v>0.04652511700987816</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3">
         <v>0.03684128448367119</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3">
         <v>0.06566676497459412</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3">
         <v>0.06749401986598969</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3">
         <v>0.06637317687273026</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3">
         <v>0.04759922251105309</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3">
         <v>0.05016208440065384</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3">
         <v>0.05959214642643929</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="3">
         <v>0.05425899103283882</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="3">
         <v>0.06161560863256454</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9" s="3">
         <v>0.06547313928604126</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="3">
         <v>0.06543613225221634</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" s="3">
         <v>0.05513908714056015</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9" s="3">
         <v>0.05830733105540276</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" s="3">
         <v>0.06137459725141525</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tends to find fault with others</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="3">
         <v>0.09308630228042603</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3">
         <v>0.09417959302663803</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3">
         <v>0.08316748589277267</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3">
         <v>0.08641235530376434</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3">
         <v>0.08945445716381073</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3">
         <v>0.06201968342065811</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3">
         <v>0.05532891675829887</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3">
         <v>0.0632651075720787</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3">
         <v>0.06577792763710022</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.06543766707181931</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="L10" s="3">
+        <v>0.0654376670718193</v>
+      </c>
+      <c r="M10" s="3">
         <v>0.06333690136671066</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3">
         <v>0.05763601139187813</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="3">
         <v>0.06207523494958878</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="3">
         <v>0.05953468754887581</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="3">
         <v>0.0548095591366291</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="3">
         <v>0.08364900201559067</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="3">
         <v>0.05883291736245155</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="3">
         <v>0.05082724243402481</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10" s="3">
         <v>0.05299947783350945</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10" s="3">
         <v>0.05667315796017647</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>is helpful and unselfish with others</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3">
         <v>0.06096208840608597</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3">
         <v>0.06017793715000153</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="3">
         <v>0.06369195878505707</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="3">
         <v>0.06416578590869904</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="3">
         <v>0.056578129529953</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="3">
         <v>0.05408993735909462</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="3">
         <v>0.001088871620595455</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="3">
         <v>0.05698569864034653</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3">
         <v>0.05225089564919472</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3">
         <v>0.06008931621909142</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3">
         <v>0.04809422045946121</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3">
         <v>0.02669769898056984</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="3">
         <v>0.05291163176298141</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="3">
         <v>0.04022336006164551</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="3">
         <v>0.04823961853981018</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11" s="3">
         <v>0.07255655527114868</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="3">
         <v>0.05906013026833534</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" s="3">
         <v>0.05217373743653297</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11" s="3">
         <v>0.05406501889228821</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11" s="3">
         <v>0.04591966420412064</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>starts quarrels with others</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3">
         <v>0.06104457378387451</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3">
         <v>0.06946956366300583</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="3">
         <v>0.05185747146606445</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="3">
         <v>0.05534955114126205</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="3">
         <v>0.05928869172930717</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="3">
         <v>0.04568466916680336</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="3">
         <v>0.04312038794159889</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3">
         <v>0.04494937509298325</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3">
         <v>0.04138793051242828</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3">
         <v>0.04734392464160919</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="3">
         <v>0.04863834008574486</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3">
         <v>0.04805511608719826</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="3">
         <v>0.0427062138915062</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="3">
         <v>0.03104057535529137</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="3">
         <v>0.04203302040696144</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12" s="3">
         <v>0.0550532229244709</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="3">
         <v>0.040070541203022</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" s="3">
         <v>0.04089532792568207</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12" s="3">
         <v>0.02592014335095882</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V12" s="3">
         <v>0.04278457909822464</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>has a forgiving nature</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3">
         <v>0.06686469167470932</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3">
         <v>0.07542363554239273</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="3">
         <v>0.05889124423265457</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="3">
         <v>0.06660234928131104</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="3">
         <v>0.0656697154045105</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="3">
         <v>0.04379582032561302</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="3">
         <v>0.03236864134669304</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="3">
         <v>0.05258876085281372</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3">
         <v>0.05062052235007286</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3">
         <v>0.05190237239003181</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="3">
         <v>0.0499914288520813</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3">
         <v>0.05058707296848297</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="3">
         <v>0.05358045548200607</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="3">
         <v>0.04349973425269127</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="3">
         <v>0.05253620073199272</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" s="3">
         <v>0.06896932423114777</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="3">
         <v>0.05590881407260895</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" s="3">
         <v>0.05165264755487442</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U13" s="3">
         <v>0.05333168804645538</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13" s="3">
         <v>0.05021675676107407</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>is generally trusting</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="3">
         <v>0.05385226756334305</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3">
         <v>0.05167323723435402</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="3">
         <v>0.05205921456217766</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="3">
         <v>0.05332290753722191</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="3">
         <v>0.05448191985487938</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="3">
         <v>0.05113320797681808</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="3">
         <v>0.04753010720014572</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="3">
         <v>0.05529792606830597</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="3">
         <v>0.05397718772292137</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="3">
         <v>0.05688647925853729</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="3">
         <v>0.04953981190919876</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="3">
         <v>0.04269054532051086</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="3">
         <v>0.05161000788211823</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="3">
         <v>0.0453033372759819</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="3">
         <v>0.05093438178300858</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" s="3">
         <v>0.05416825413703918</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="3">
         <v>0.05510084331035614</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14" s="3">
         <v>0.04482584819197655</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U14" s="3">
         <v>0.05684532970190048</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V14" s="3">
         <v>0.04931098595261574</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>can be cold and aloof</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="3">
         <v>0.03155335411429405</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3">
         <v>0.03623712435364723</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="3">
         <v>0.03427321836352348</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="3">
         <v>0.03937828540802002</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="3">
         <v>0.03139786422252655</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="3">
         <v>0.01597430557012558</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3">
         <v>0.01541309431195259</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="3">
         <v>0.02141163684427738</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="3">
         <v>0.02607862465083599</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="3">
         <v>0.02481912262737751</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="3">
         <v>0.01779764890670776</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="3">
         <v>0.02069328911602497</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="3">
         <v>0.02471863850951195</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="3">
         <v>0.02144166268408298</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="3">
         <v>0.02583137154579163</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="3">
         <v>0.0400603711605072</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="3">
         <v>0.02349554188549519</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" s="3">
         <v>0.02143916301429272</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U15" s="3">
         <v>0.02106420323252678</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V15" s="3">
         <v>0.0254353154450655</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>is considerate and kind to almost everyone</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3">
         <v>0.07975427806377411</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3">
         <v>0.07756397128105164</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3">
         <v>0.06677163392305374</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="3">
         <v>0.07898380607366562</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3">
         <v>0.08312813192605972</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3">
         <v>0.07025404274463654</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3">
         <v>0.08538946509361267</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="3">
         <v>0.05985688045620918</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3">
         <v>0.06509898602962494</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3">
         <v>0.0624602846801281</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="3">
         <v>0.05794476345181465</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="3">
         <v>0.05527937039732933</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="3">
         <v>0.0497807152569294</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="3">
         <v>0.04806318506598473</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="3">
         <v>0.04229233413934708</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16" s="3">
         <v>0.0709829106926918</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16" s="3">
         <v>0.05566330626606941</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" s="3">
         <v>0.04556579887866974</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U16" s="3">
         <v>0.05156505852937698</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V16" s="3">
         <v>0.06482962518930435</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>is sometimes rude to others</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3">
         <v>0.06920979171991348</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3">
         <v>0.0790102407336235</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="3">
         <v>0.06463015824556351</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="3">
         <v>0.07496556639671326</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="3">
         <v>0.05999541655182838</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="3">
         <v>0.04869742691516876</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3">
         <v>0.04890339076519012</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="3">
         <v>0.05265884101390839</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="3">
         <v>0.05508560687303543</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="3">
         <v>0.05506286770105362</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="3">
         <v>0.04790861159563065</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="3">
         <v>0.04800072312355042</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="3">
         <v>0.05368302762508392</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="3">
         <v>0.04893819615244865</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="3">
         <v>0.0480949841439724</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17" s="3">
         <v>0.06809216737747192</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" s="3">
         <v>0.04789662733674049</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" s="3">
         <v>0.0450904592871666</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U17" s="3">
         <v>0.04067123308777809</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V17" s="3">
         <v>0.04117587581276894</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>likes to cooperate with others</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Agreeableness</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="3">
         <v>0.04177848622202873</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3">
         <v>0.05967671424150467</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="3">
         <v>0.04470879584550858</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="3">
         <v>0.05017072707414627</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="3">
         <v>0.04308680444955826</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="3">
         <v>0.02305839210748672</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3">
         <v>0.03047473356127739</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="3">
         <v>0.03336871415376663</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="3">
         <v>0.03661821782588959</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="3">
         <v>0.03215304017066956</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="3">
         <v>0.03481548279523849</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3">
         <v>0.04326805472373962</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="3">
         <v>0.04195058345794678</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="3">
         <v>0.04310044646263123</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="3">
         <v>0.03936272859573364</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18" s="3">
         <v>0.05109609663486481</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="3">
         <v>0.03350841253995895</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18" s="3">
         <v>0.0389903336763382</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U18" s="3">
         <v>0.0372370071709156</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V18" s="3">
         <v>0.03438008576631546</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>does a thorough job</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3">
         <v>0.07092297822237015</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3">
         <v>0.0868445411324501</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="3">
         <v>0.07645963877439499</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="3">
         <v>0.08003637939691544</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="3">
         <v>0.0817667692899704</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="3">
         <v>0.04302956908941269</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3">
         <v>0.05554695427417755</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="3">
         <v>0.05321311578154564</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="3">
         <v>0.05269081518054008</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="3">
         <v>0.05389560014009476</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="3">
         <v>0.05189412087202072</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="3">
         <v>0.05814485996961594</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="3">
         <v>0.06446227431297302</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="3">
         <v>0.05424202978610992</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="3">
         <v>0.05949036777019501</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.07523480802774429</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R19" s="3">
+        <v>0.0752348080277443</v>
+      </c>
+      <c r="S19" s="3">
         <v>0.05343043431639671</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" s="3">
         <v>0.05164673924446106</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U19" s="3">
         <v>0.05417188629508018</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V19" s="3">
         <v>0.05826978757977486</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>can be somewhat careless</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="3">
         <v>0.05568352341651917</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3">
         <v>0.06294652074575424</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="3">
         <v>0.06358680874109268</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="3">
         <v>0.06593162566423416</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3">
         <v>0.06259304285049438</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3">
         <v>0.05800135433673859</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3">
         <v>0.05991747230291367</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="3">
         <v>0.07126646488904953</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="3">
         <v>0.0711127445101738</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="3">
         <v>0.06846030056476593</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="3">
         <v>0.06361842900514603</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3">
         <v>0.05840612202882767</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="3">
         <v>0.07044203579425812</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="3">
         <v>0.06770632416009903</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="3">
         <v>0.06902740150690079</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20" s="3">
         <v>0.06685420125722885</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="3">
         <v>0.07106167823076248</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" s="3">
         <v>0.0648358091711998</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U20" s="3">
         <v>0.06145447492599487</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V20" s="3">
         <v>0.06356224417686462</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>is a reliable worker</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3">
         <v>0.07741671055555344</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3">
         <v>0.08465077728033066</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="3">
         <v>0.08003904670476913</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="3">
         <v>0.08238181471824646</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="3">
         <v>0.08591211587190628</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="3">
         <v>0.04551604017615318</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="3">
         <v>0.03684009611606598</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="3">
         <v>0.0643596425652504</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3">
         <v>0.0608438216149807</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3">
         <v>0.06131934002041817</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="3">
         <v>0.05129474028944969</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3">
         <v>0.04818668961524963</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="3">
         <v>0.06191098690032959</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="3">
         <v>0.05681122094392776</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="3">
         <v>0.0564119890332222</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21" s="3">
         <v>0.07883172482252121</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="3">
         <v>0.06141592934727669</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T21" s="3">
         <v>0.05098916217684746</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U21" s="3">
         <v>0.05919951200485229</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V21" s="3">
         <v>0.04770088195800781</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>tends to be disorganized</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="3">
         <v>0.05527074635028839</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3">
         <v>0.06340384483337402</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="3">
         <v>0.05808877944946289</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="3">
         <v>0.0570618100464344</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="3">
         <v>0.05977176874876022</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="3">
         <v>0.04156838729977608</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="3">
         <v>0.04835209995508194</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="3">
         <v>0.05014890059828758</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="3">
         <v>0.04350985214114189</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3">
         <v>0.05086508020758629</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="3">
         <v>0.0380231998860836</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="3">
         <v>0.04444767534732819</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="3">
         <v>0.04418804123997688</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="3">
         <v>0.04088729247450829</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="3">
         <v>0.04411395639181137</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22" s="3">
         <v>0.05748127028346062</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="3">
         <v>0.04834423586726189</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" s="3">
         <v>0.04172942787408829</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U22" s="3">
         <v>0.04687964916229248</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V22" s="3">
         <v>0.05161513015627861</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>tends to be lazy</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="3">
         <v>0.03593956306576729</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3">
         <v>0.0434851162135601</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="3">
         <v>0.04119629040360451</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="3">
         <v>0.0461449921131134</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="3">
         <v>0.04105909913778305</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="3">
         <v>0.03122712671756744</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="3">
         <v>0.02724014036357403</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="3">
         <v>0.03561471402645111</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="3">
         <v>0.03864600136876106</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3">
         <v>0.03820298612117767</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="3">
         <v>0.03438351303339005</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="3">
         <v>0.03954122960567474</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="3">
         <v>0.04262750223278999</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="3">
         <v>0.04369504377245903</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23" s="3">
         <v>0.04263526946306229</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23" s="3">
         <v>0.0446418821811676</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="3">
         <v>0.03826306760311127</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" s="3">
         <v>0.04095486551523209</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U23" s="3">
         <v>0.04579651355743408</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V23" s="3">
         <v>0.04958454146981239</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>perseveres until the task is finished</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="3">
         <v>0.04285083338618279</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3">
         <v>0.04750461503863335</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="3">
         <v>0.0504801943898201</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="3">
         <v>0.04819624498486519</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="3">
         <v>0.05466390773653984</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="3">
         <v>0.03623387962579727</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="3">
         <v>0.0252127218991518</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="3">
         <v>0.04215016216039658</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="3">
         <v>0.04457505792379379</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3">
         <v>0.04409132897853851</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="3">
         <v>0.04195950552821159</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="3">
         <v>0.03843051567673683</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="3">
         <v>0.04949138686060905</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24" s="3">
         <v>0.04423744976520538</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" s="3">
         <v>0.0437854677438736</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R24" s="3">
         <v>0.05556831136345863</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24" s="3">
         <v>0.04198653623461723</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T24" s="3">
         <v>0.04003307223320007</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U24" s="3">
         <v>0.04597650095820427</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V24" s="3">
         <v>0.04908082261681557</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>does things efficiently</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="3">
         <v>0.05086477845907211</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3">
         <v>0.05827320367097855</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="3">
         <v>0.05547056719660759</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="3">
         <v>0.05343639850616455</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="3">
         <v>0.05450224876403809</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="3">
         <v>0.05510332062840462</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="3">
         <v>0.04800169914960861</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="3">
         <v>0.0612727478146553</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="3">
         <v>0.06302426755428314</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3">
         <v>0.06497379392385483</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="3">
         <v>0.06089957058429718</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="3">
         <v>0.06063668057322502</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="3">
         <v>0.06443329155445099</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="3">
         <v>0.06200312823057175</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" s="3">
         <v>0.06887058168649673</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R25" s="3">
         <v>0.05682945996522903</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" s="3">
         <v>0.06180264055728912</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T25" s="3">
         <v>0.06301726400852203</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U25" s="3">
         <v>0.0619967021048069</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V25" s="3">
         <v>0.06788225471973419</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>makes plans and follows through with them</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3">
         <v>0.06190889701247215</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3">
         <v>0.07031510770320892</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="3">
         <v>0.06157661229372025</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="3">
         <v>0.06079602986574173</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="3">
         <v>0.06678753346204758</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="3">
         <v>0.06004307419061661</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="3">
         <v>0.04530763626098633</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="3">
         <v>0.05203212052583694</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="3">
         <v>0.05766170099377632</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3">
         <v>0.05372783169150352</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="3">
         <v>0.06248462945222855</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="3">
         <v>0.0628986731171608</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="3">
         <v>0.05620377883315086</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="3">
         <v>0.05165714770555496</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26" s="3">
         <v>0.05370797961950302</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R26" s="3">
         <v>0.06445474922657013</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26" s="3">
         <v>0.0537770614027977</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T26" s="3">
         <v>0.05565264821052551</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U26" s="3">
         <v>0.05681662261486053</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V26" s="3">
         <v>0.04482579231262207</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>is easily distracted</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Conscientiousness</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3">
         <v>0.05550887435674667</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3">
         <v>0.05618337169289589</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="3">
         <v>0.06037354469299316</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="3">
         <v>0.0567755252122879</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="3">
         <v>0.0585925281047821</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3">
         <v>0.05119961872696877</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="3">
         <v>0.04742181673645973</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="3">
         <v>0.06151574850082397</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="3">
         <v>0.05777045339345932</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3">
         <v>0.06076027825474739</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="3">
         <v>0.05608770623803139</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="3">
         <v>0.04860430583357811</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="3">
         <v>0.06547853350639343</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="3">
         <v>0.06002994626760483</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27" s="3">
         <v>0.06257690489292145</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R27" s="3">
         <v>0.06120708957314491</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S27" s="3">
         <v>0.06149968132376671</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T27" s="3">
         <v>0.05679577961564064</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U27" s="3">
         <v>0.05628659576177597</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V27" s="3">
         <v>0.05998899042606354</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>is depressed, blue</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="3">
         <v>0.07052730768918991</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3">
         <v>0.08234023302793503</v>
       </c>
-      <c r="E28" t="n">
-        <v>0.08408245444297791</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="E28" s="3">
+        <v>0.0840824544429779</v>
+      </c>
+      <c r="F28" s="3">
         <v>0.0870315358042717</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="3">
         <v>0.0815097987651825</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="3">
         <v>0.05163615942001343</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="3">
         <v>0.04775033891201019</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="3">
         <v>0.0676715150475502</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="3">
         <v>0.07141873240470886</v>
       </c>
-      <c r="L28" t="n">
-        <v>0.06782772392034531</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="L28" s="3">
+        <v>0.0678277239203453</v>
+      </c>
+      <c r="M28" s="3">
         <v>0.03756236284971237</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="3">
         <v>0.03523396700620651</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="3">
         <v>0.04560297727584839</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28" s="3">
         <v>0.03859782218933105</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" s="3">
         <v>0.0477646067738533</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R28" s="3">
         <v>0.08801998198032379</v>
       </c>
-      <c r="S28" t="n">
-        <v>0.06958490610122681</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="S28" s="3">
+        <v>0.0695849061012268</v>
+      </c>
+      <c r="T28" s="3">
         <v>0.04712551459670067</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U28" s="3">
         <v>0.07127310335636139</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V28" s="3">
         <v>0.06121814623475075</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>is relaxed, handles stress well</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="3">
         <v>0.02309689484536648</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3">
         <v>0.04500937089323997</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="3">
         <v>0.02958342432975769</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="3">
         <v>0.03689376264810562</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="3">
         <v>0.03445021435618401</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="3">
         <v>0.008366022258996964</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="3">
         <v>0.01315937750041485</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="3">
         <v>0.02040413953363895</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="3">
         <v>0.01940578781068325</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3">
         <v>0.01941830478608608</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="3">
         <v>0.01706176437437534</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="3">
         <v>0.02465206198394299</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="3">
         <v>0.02434305660426617</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="3">
         <v>0.02053791284561157</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="3">
         <v>0.02516209334135056</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R29" s="3">
         <v>0.02920463308691978</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="3">
         <v>0.01882277987897396</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T29" s="3">
         <v>0.02262003347277641</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U29" s="3">
         <v>0.02217671275138855</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V29" s="3">
         <v>0.02007493562996387</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>can be tense</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="3">
         <v>0.06344722956418991</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3">
         <v>0.06623969972133636</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="3">
         <v>0.06818125396966934</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="3">
         <v>0.06553395837545395</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="3">
         <v>0.07091349363327026</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="3">
         <v>0.04713615030050278</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="3">
         <v>0.05713290721178055</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="3">
         <v>0.06285711377859116</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="3">
         <v>0.06126857548952103</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3">
         <v>0.06140226125717163</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="3">
         <v>0.05774875730276108</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="3">
         <v>0.06100490689277649</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="3">
         <v>0.0663808137178421</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="3">
         <v>0.06306688487529755</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="3">
         <v>0.06694324314594269</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R30" s="3">
         <v>0.07043788582086563</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="3">
         <v>0.06346210092306137</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T30" s="3">
         <v>0.06062008440494537</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U30" s="3">
         <v>0.06575612723827362</v>
       </c>
-      <c r="V30" t="n">
+      <c r="V30" s="3">
         <v>0.06131423637270927</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>worries a lot</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="3">
         <v>0.06224064156413078</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3">
         <v>0.06791872531175613</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="3">
         <v>0.06720218062400818</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="3">
         <v>0.0659913644194603</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="3">
         <v>0.07358606159687042</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="3">
         <v>0.03387067094445229</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="3">
         <v>0.03654878586530685</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="3">
         <v>0.04534222930669785</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="3">
         <v>0.04150504991412163</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="3">
         <v>0.04360433295369148</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="3">
         <v>0.04143340140581131</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="3">
         <v>0.03123845718801022</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" s="3">
         <v>0.04697922989726067</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31" s="3">
         <v>0.04063888639211655</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="3">
         <v>0.04763880744576454</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R31" s="3">
         <v>0.06718109548091888</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S31" s="3">
         <v>0.04656733945012093</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T31" s="3">
         <v>0.04518062993884087</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U31" s="3">
         <v>0.04315857961773872</v>
       </c>
-      <c r="V31" t="n">
+      <c r="V31" s="3">
         <v>0.04641880467534065</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>is emotionally stable, not easily upset</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="3">
         <v>0.06504296511411667</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3">
         <v>0.08202583342790604</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="3">
         <v>0.06644979864358902</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="3">
         <v>0.07701481133699417</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="3">
         <v>0.06996507197618484</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="3">
         <v>0.04505139589309692</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="3">
         <v>0.03254881128668785</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="3">
         <v>0.06082535535097122</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" s="3">
         <v>0.05648525059223175</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="3">
         <v>0.05487474799156189</v>
       </c>
-      <c r="M32" t="n">
-        <v>0.06876701861619949</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="M32" s="3">
+        <v>0.0687670186161995</v>
+      </c>
+      <c r="N32" s="3">
         <v>0.05923439562320709</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="3">
         <v>0.0804816260933876</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32" s="3">
         <v>0.07664753496646881</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32" s="3">
         <v>0.07016272842884064</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R32" s="3">
         <v>0.071316197514534</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S32" s="3">
         <v>0.0528937354683876</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T32" s="3">
         <v>0.06382270902395248</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U32" s="3">
         <v>0.03867862373590469</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V32" s="3">
         <v>0.05567989870905876</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>can be moody</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="3">
         <v>0.04076596349477768</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3">
         <v>0.05142776668071747</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="3">
         <v>0.05333864688873291</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="3">
         <v>0.05544079095125198</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="3">
         <v>0.05442412197589874</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="3">
         <v>0.01535324566066265</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="3">
         <v>0.009284982457756996</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="3">
         <v>0.0336802713572979</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" s="3">
         <v>0.03015064261853695</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3">
         <v>0.03265850618481636</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="3">
         <v>0.0261884517967701</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="3">
         <v>0.02192018181085587</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="3">
         <v>0.04030654206871986</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33" s="3">
         <v>0.03660499304533005</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" s="3">
         <v>0.04005718231201172</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R33" s="3">
         <v>0.05449935048818588</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" s="3">
         <v>0.03480081260204315</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T33" s="3">
         <v>0.03045844100415707</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U33" s="3">
         <v>0.03635251894593239</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V33" s="3">
         <v>0.03583009168505669</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>remains calm in tense situations</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="3">
         <v>0.07443996518850327</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3">
         <v>0.07492808997631073</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="3">
         <v>0.07633868604898453</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="3">
         <v>0.0761808305978775</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="3">
         <v>0.07871665805578232</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="3">
         <v>0.05440869182348251</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="3">
         <v>0.0368046946823597</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="3">
         <v>0.06233541294932365</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34" s="3">
         <v>0.05802801251411438</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34" s="3">
         <v>0.06197674572467804</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="3">
         <v>0.06037430465221405</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" s="3">
         <v>0.04753776267170906</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" s="3">
         <v>0.06629678606987</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34" s="3">
         <v>0.06181993708014488</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34" s="3">
         <v>0.0676301047205925</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R34" s="3">
         <v>0.08040289580821991</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S34" s="3">
         <v>0.06373128294944763</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T34" s="3">
         <v>0.06234639137983322</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U34" s="3">
         <v>0.06593659520149231</v>
       </c>
-      <c r="V34" t="n">
+      <c r="V34" s="3">
         <v>0.06994874030351639</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>gets nervous easily</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Neuroticism</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="3">
         <v>0.03367352485656738</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3">
         <v>0.03970513492822647</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="3">
         <v>0.04207142069935799</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="3">
         <v>0.04512806236743927</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="3">
         <v>0.03413582220673561</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="3">
         <v>0.03128752112388611</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="3">
         <v>-0.002090937225148082</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="3">
         <v>0.03788687288761139</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35" s="3">
         <v>0.03441886976361275</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35" s="3">
         <v>0.03871232271194458</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="3">
         <v>0.03412441164255142</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" s="3">
         <v>0.01863485015928745</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="3">
         <v>0.04196184128522873</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35" s="3">
         <v>0.03362135589122772</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35" s="3">
         <v>0.04353662952780724</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R35" s="3">
         <v>0.0451582707464695</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S35" s="3">
         <v>0.04068073630332947</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T35" s="3">
         <v>0.03271343559026718</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U35" s="3">
         <v>0.0502491407096386</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V35" s="3">
         <v>0.0503927618265152</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>is original, comes up with new ideas</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="3">
         <v>0.0445607416331768</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3">
         <v>0.05169693380594254</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="3">
         <v>0.03868784382939339</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="3">
         <v>0.04153517633676529</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" s="3">
         <v>0.04097702354192734</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="3">
         <v>0.04080038517713547</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="3">
         <v>0.03614872694015503</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="3">
         <v>0.04003040492534637</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36" s="3">
         <v>0.04432237520813942</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36" s="3">
         <v>0.04540669918060303</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="3">
         <v>0.03549332171678543</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" s="3">
         <v>0.04447838664054871</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" s="3">
         <v>0.0391232930123806</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P36" s="3">
         <v>0.04002983495593071</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36" s="3">
         <v>0.04199014976620674</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R36" s="3">
         <v>0.04165849089622498</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S36" s="3">
         <v>0.03913029283285141</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T36" s="3">
         <v>0.03734564781188965</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U36" s="3">
         <v>0.03940948098897934</v>
       </c>
-      <c r="V36" t="n">
+      <c r="V36" s="3">
         <v>0.02910007163882256</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>is curious about many different things</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="3">
         <v>0.1018679663538933</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3">
         <v>0.1059979274868965</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="3">
         <v>0.09784972667694092</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="3">
         <v>0.1013874113559723</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="3">
         <v>0.107510469853878</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="3">
         <v>0.0715193897485733</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="3">
         <v>0.05806522443890572</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="3">
         <v>0.07939360290765762</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37" s="3">
         <v>0.07860114425420761</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37" s="3">
         <v>0.08258131146430969</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="3">
         <v>0.0673692598938942</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" s="3">
         <v>0.06086070835590363</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="3">
         <v>0.07345209270715714</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37" s="3">
         <v>0.06172023713588715</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37" s="3">
         <v>0.07301095128059387</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R37" s="3">
         <v>0.1015879139304161</v>
       </c>
-      <c r="S37" t="n">
-        <v>0.07938613742589951</v>
-      </c>
-      <c r="T37" t="n">
+      <c r="S37" s="3">
+        <v>0.0793861374258995</v>
+      </c>
+      <c r="T37" s="3">
         <v>0.07288271933794022</v>
       </c>
-      <c r="U37" t="n">
+      <c r="U37" s="3">
         <v>0.07133538275957108</v>
       </c>
-      <c r="V37" t="n">
+      <c r="V37" s="3">
         <v>0.06985059380531311</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>is ingenious, a deep thinker</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="3">
         <v>0.03598418086767197</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3">
         <v>0.03390705585479736</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="3">
         <v>0.03327865153551102</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="3">
         <v>0.03592710942029953</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="3">
         <v>0.02990369684994221</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="3">
         <v>0.04785255715250969</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="3">
         <v>0.04253029823303223</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="3">
         <v>0.04429890215396881</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38" s="3">
         <v>0.05151072889566422</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38" s="3">
         <v>0.0482594408094883</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="3">
         <v>0.04238763451576233</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" s="3">
         <v>0.03988201916217804</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" s="3">
         <v>0.04447478428483009</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38" s="3">
         <v>0.04132538288831711</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38" s="3">
         <v>0.04203354567289352</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R38" s="3">
         <v>0.04098152369260788</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S38" s="3">
         <v>0.04573161900043488</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T38" s="3">
         <v>0.04276608675718307</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U38" s="3">
         <v>0.0497182235121727</v>
       </c>
-      <c r="V38" t="n">
+      <c r="V38" s="3">
         <v>0.03946313261985779</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>has an active imagination</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="3">
         <v>0.04620067402720451</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3">
         <v>0.05537459254264832</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="3">
         <v>0.05007727816700935</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="3">
         <v>0.05116851627826691</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="3">
         <v>0.05543209984898567</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="3">
         <v>0.04889778792858124</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="3">
         <v>0.0603889599442482</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="3">
         <v>0.0654793456196785</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39" s="3">
         <v>0.0637534037232399</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39" s="3">
         <v>0.0650303065776825</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="3">
         <v>0.05845742672681808</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" s="3">
         <v>0.07340405881404877</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="3">
         <v>0.06373243778944016</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39" s="3">
         <v>0.05713482946157455</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39" s="3">
         <v>0.06825793534517288</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R39" s="3">
         <v>0.04849419742822647</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S39" s="3">
         <v>0.06524024158716202</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T39" s="3">
         <v>0.06326741725206375</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U39" s="3">
         <v>0.05844099447131157</v>
       </c>
-      <c r="V39" t="n">
+      <c r="V39" s="3">
         <v>0.06105873733758926</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>is inventive</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="3">
         <v>0.06773538142442703</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3">
         <v>0.07469026744365692</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="3">
         <v>0.07527483254671097</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="3">
         <v>0.07551563531160355</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="3">
         <v>0.08047523349523544</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="3">
         <v>0.05356424301862717</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="3">
         <v>0.07535966485738754</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" s="3">
         <v>0.0643211305141449</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40" s="3">
         <v>0.06745120137929916</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40" s="3">
         <v>0.0646405890583992</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="3">
         <v>0.04762290418148041</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" s="3">
         <v>0.0645739808678627</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="3">
         <v>0.0590166300535202</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40" s="3">
         <v>0.05777991563081741</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40" s="3">
         <v>0.06034061312675476</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R40" s="3">
         <v>0.07602118700742722</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S40" s="3">
         <v>0.06325522065162659</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T40" s="3">
         <v>0.05274227261543274</v>
       </c>
-      <c r="U40" t="n">
+      <c r="U40" s="3">
         <v>0.06703999638557434</v>
       </c>
-      <c r="V40" t="n">
+      <c r="V40" s="3">
         <v>0.06734407693147659</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>values artistic, aesthetic experiences</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="3">
         <v>0.03040705062448978</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3">
         <v>0.03775272518396378</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="3">
         <v>0.04126189276576042</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="3">
         <v>0.03845052793622017</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="3">
         <v>0.0381295457482338</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="3">
         <v>0.03532018139958382</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="3">
         <v>0.03160426020622253</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="3">
         <v>0.0410974882543087</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41" s="3">
         <v>0.03554488345980644</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41" s="3">
         <v>0.03932405263185501</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="3">
         <v>0.03379210829734802</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" s="3">
         <v>0.02879555150866508</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" s="3">
         <v>0.04228616878390312</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P41" s="3">
         <v>0.02804373949766159</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41" s="3">
         <v>0.0371721163392067</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R41" s="3">
         <v>0.04116378352046013</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S41" s="3">
         <v>0.03816478699445724</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T41" s="3">
         <v>0.03008241951465607</v>
       </c>
-      <c r="U41" t="n">
+      <c r="U41" s="3">
         <v>0.04143539443612099</v>
       </c>
-      <c r="V41" t="n">
+      <c r="V41" s="3">
         <v>0.02587859146296978</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>prefers work that is routine</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="3">
         <v>0.09771264344453812</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3">
         <v>0.1116870492696762</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="3">
         <v>0.09705311805009842</v>
       </c>
-      <c r="F42" t="n">
-        <v>0.09809102118015289</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="F42" s="3">
+        <v>0.0980910211801529</v>
+      </c>
+      <c r="G42" s="3">
         <v>0.1051329076290131</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="3">
         <v>0.06174932792782784</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="3">
         <v>0.08910714089870453</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" s="3">
         <v>0.07308600842952728</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42" s="3">
         <v>0.07697369903326035</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" s="3">
         <v>0.07270525395870209</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" s="3">
         <v>0.06536763906478882</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42" s="3">
         <v>0.0854652151465416</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42" s="3">
         <v>0.08227252960205078</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P42" s="3">
         <v>0.0790698304772377</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42" s="3">
         <v>0.07570787519216537</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R42" s="3">
         <v>0.09310586005449295</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S42" s="3">
         <v>0.06999684870243073</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T42" s="3">
         <v>0.07448585331439972</v>
       </c>
-      <c r="U42" t="n">
+      <c r="U42" s="3">
         <v>0.06887752562761307</v>
       </c>
-      <c r="V42" t="n">
+      <c r="V42" s="3">
         <v>0.06811320781707764</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>likes to reflect, play with ideas</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+      <c r="A43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="3">
         <v>0.03474771976470947</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3">
         <v>0.03322266787290573</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="3">
         <v>0.03363916277885437</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="3">
         <v>0.02746047824621201</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="3">
         <v>0.02920723892748356</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3">
         <v>0.04265058785676956</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="3">
         <v>0.01756908558309078</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="3">
         <v>0.03029519878327847</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43" s="3">
         <v>0.03312936797738075</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43" s="3">
         <v>0.03752260655164719</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="3">
         <v>0.03879499435424805</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43" s="3">
         <v>0.02996287308633327</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43" s="3">
         <v>0.0313061848282814</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43" s="3">
         <v>0.0281048733741045</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43" s="3">
         <v>0.03098594583570957</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R43" s="3">
         <v>0.0387321263551712</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S43" s="3">
         <v>0.03172726184129715</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T43" s="3">
         <v>0.03081101924180984</v>
       </c>
-      <c r="U43" t="n">
+      <c r="U43" s="3">
         <v>0.04006831720471382</v>
       </c>
-      <c r="V43" t="n">
+      <c r="V43" s="3">
         <v>0.03002695180475712</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>is sophisticated in art, music, or literature</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Openness</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+      <c r="A44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="3">
         <v>0.0115935979411006</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3">
         <v>0.01893415115773678</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="3">
         <v>0.02112420089542866</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="3">
         <v>0.02130595222115517</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="3">
         <v>0.02314626798033714</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="3">
         <v>0.01983807049691677</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="3">
         <v>0.004466659389436245</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" s="3">
         <v>0.0157715305685997</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44" s="3">
         <v>0.01722562871873379</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44" s="3">
         <v>0.01673968695104122</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" s="3">
         <v>0.01678695343434811</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44" s="3">
         <v>0.01625247672200203</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O44" s="3">
         <v>0.0203300453722477</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P44" s="3">
         <v>0.01849702373147011</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44" s="3">
         <v>0.01459266431629658</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R44" s="3">
         <v>0.02390458434820175</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S44" s="3">
         <v>0.01514348480850458</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T44" s="3">
         <v>0.01230782456696033</v>
       </c>
-      <c r="U44" t="n">
+      <c r="U44" s="3">
         <v>0.01318280771374702</v>
       </c>
-      <c r="V44" t="n">
+      <c r="V44" s="3">
         <v>0.008058587089180946</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/siglip_out_female.xlsx
+++ b/siglip_out_female.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="85">
   <si>
     <t>Trait</t>
   </si>
@@ -22,64 +22,109 @@
     <t>Group</t>
   </si>
   <si>
-    <t>Modified\woman1\woman1_heavy_build.png</t>
-  </si>
-  <si>
-    <t>Modified\woman1\woman1_muscular.png</t>
-  </si>
-  <si>
-    <t>Modified\woman1\woman1_no_makeup.png</t>
-  </si>
-  <si>
-    <t>Modified\woman1\woman1_short_hair.png</t>
-  </si>
-  <si>
-    <t>Modified\woman1\woman1_tall.png</t>
-  </si>
-  <si>
-    <t>Modified\woman2\woman2_heavy_build.png</t>
-  </si>
-  <si>
-    <t>Modified\woman2\woman2_muscular.png</t>
-  </si>
-  <si>
-    <t>Modified\woman2\woman2_no_makeup.png</t>
-  </si>
-  <si>
-    <t>Modified\woman2\woman2_short_hair.png</t>
-  </si>
-  <si>
-    <t>Modified\woman2\woman2_tall.png</t>
-  </si>
-  <si>
-    <t>Modified\woman3\woman3_heavy_build.png</t>
-  </si>
-  <si>
-    <t>Modified\woman3\woman3_muscular.png</t>
-  </si>
-  <si>
-    <t>Modified\woman3\woman3_no_makeup.png</t>
-  </si>
-  <si>
-    <t>Modified\woman3\woman3_short_hair.png</t>
-  </si>
-  <si>
-    <t>Modified\woman3\woman3_tall.png</t>
-  </si>
-  <si>
-    <t>woman1_original.jpg</t>
-  </si>
-  <si>
-    <t>woman2_original.png</t>
-  </si>
-  <si>
-    <t>woman3_original.jpg</t>
-  </si>
-  <si>
-    <t>woman4_original.jpg</t>
-  </si>
-  <si>
-    <t>woman5_original.jpg</t>
+    <t>female1\female1_have_jewerly.png</t>
+  </si>
+  <si>
+    <t>female1\female1_have_makeup.png</t>
+  </si>
+  <si>
+    <t>female1\female1_long_hair.png</t>
+  </si>
+  <si>
+    <t>female1\female1_no_jewerly.png</t>
+  </si>
+  <si>
+    <t>female1\female1_no_makeup.png</t>
+  </si>
+  <si>
+    <t>female1\female1_short_hair.png</t>
+  </si>
+  <si>
+    <t>female1\woman1_cropped.jpg</t>
+  </si>
+  <si>
+    <t>female2\female2_have_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female2\female2_have_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female2\female2_long_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female2\female2_no_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female2\female2_no_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female2\female2_short_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female2\woman2_cropped.png</t>
+  </si>
+  <si>
+    <t>female3\female3_have_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female3\female3_have_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female3\female3_long_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female3\female3_no_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female3\female3_no_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female3\female3_short_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female3\woman3_cropped.jpg</t>
+  </si>
+  <si>
+    <t>female4\female4_have_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female4\female4_have_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female4\female4_long_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female4\female4_no_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female4\female4_no_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female4\female4_short_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female4\woman4_cropped.jpg</t>
+  </si>
+  <si>
+    <t>female5\female5_have_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female5\female5_have_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female5\female5_long_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female5\female5_no_jewerly.jpeg</t>
+  </si>
+  <si>
+    <t>female5\female5_no_makeup.jpeg</t>
+  </si>
+  <si>
+    <t>female5\female5_short_hair.jpeg</t>
+  </si>
+  <si>
+    <t>female5\woman5_cropped.jpg</t>
   </si>
   <si>
     <t>is talkative</t>
@@ -592,7 +637,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -617,6 +662,21 @@
     <col min="20" max="20" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -686,2929 +746,4909 @@
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3">
-        <v>0.04819560050964355</v>
+        <v>0.03661535680294037</v>
       </c>
       <c r="D2" s="3">
-        <v>0.05369172245264053</v>
+        <v>0.04646538197994232</v>
       </c>
       <c r="E2" s="3">
-        <v>0.05409809201955795</v>
+        <v>0.03560324013233185</v>
       </c>
       <c r="F2" s="3">
-        <v>0.05920938402414322</v>
+        <v>0.04783706367015839</v>
       </c>
       <c r="G2" s="3">
-        <v>0.05399888753890991</v>
+        <v>0.04502172768115997</v>
       </c>
       <c r="H2" s="3">
-        <v>0.05065952986478806</v>
+        <v>0.04305363446474075</v>
       </c>
       <c r="I2" s="3">
-        <v>0.03541335836052895</v>
+        <v>0.05109300091862679</v>
       </c>
       <c r="J2" s="3">
-        <v>0.05356951430439949</v>
+        <v>0.05392241105437279</v>
       </c>
       <c r="K2" s="3">
-        <v>0.05267328768968582</v>
+        <v>0.05700952187180519</v>
       </c>
       <c r="L2" s="3">
-        <v>0.05498738959431648</v>
+        <v>0.04987803846597672</v>
       </c>
       <c r="M2" s="3">
-        <v>0.04990476369857788</v>
+        <v>0.05569629371166229</v>
       </c>
       <c r="N2" s="3">
-        <v>0.04740092530846596</v>
+        <v>0.05928023904561996</v>
       </c>
       <c r="O2" s="3">
-        <v>0.06108781695365906</v>
+        <v>0.05324548482894897</v>
       </c>
       <c r="P2" s="3">
-        <v>0.0534418597817421</v>
+        <v>0.05730529502034187</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.06043826416134834</v>
+        <v>0.0417967215180397</v>
       </c>
       <c r="R2" s="3">
-        <v>0.05663044005632401</v>
+        <v>0.06362830102443695</v>
       </c>
       <c r="S2" s="3">
-        <v>0.05659561976790428</v>
+        <v>0.05893989652395248</v>
       </c>
       <c r="T2" s="3">
-        <v>0.05560531839728355</v>
+        <v>0.04226801916956902</v>
       </c>
       <c r="U2" s="3">
-        <v>0.05932139232754707</v>
+        <v>0.04945605620741844</v>
       </c>
       <c r="V2" s="3">
-        <v>0.06234120577573776</v>
+        <v>0.05356393754482269</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0.05034651234745979</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0.03830570727586746</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>0.03910839930176735</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>0.04522766545414925</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>0.04389908164739609</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0.04251685366034508</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0.05578474327921867</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0.04097404330968857</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>0.05014939233660698</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>0.06058222055435181</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>0.04776801541447639</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>0.05589612945914268</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>0.05228601768612862</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>0.06234583631157875</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>0.06049497798085213</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3">
-        <v>0.03479139506816864</v>
+        <v>0.02583710290491581</v>
       </c>
       <c r="D3" s="3">
-        <v>0.04033245146274567</v>
+        <v>0.03104456700384617</v>
       </c>
       <c r="E3" s="3">
-        <v>0.04519659280776978</v>
+        <v>0.01789956539869308</v>
       </c>
       <c r="F3" s="3">
-        <v>0.04558618739247322</v>
+        <v>0.02909613400697708</v>
       </c>
       <c r="G3" s="3">
-        <v>0.04598721489310265</v>
+        <v>0.02683768607676029</v>
       </c>
       <c r="H3" s="3">
-        <v>0.02467936836183071</v>
+        <v>0.02827253378927708</v>
       </c>
       <c r="I3" s="3">
-        <v>0.02066670544445515</v>
+        <v>0.03231283277273178</v>
       </c>
       <c r="J3" s="3">
-        <v>0.03479605168104172</v>
+        <v>0.03717676177620888</v>
       </c>
       <c r="K3" s="3">
-        <v>0.03543921560049057</v>
+        <v>0.04511114209890366</v>
       </c>
       <c r="L3" s="3">
-        <v>0.03599001094698906</v>
+        <v>0.03430384397506714</v>
       </c>
       <c r="M3" s="3">
-        <v>0.02786770462989807</v>
+        <v>0.04203608632087708</v>
       </c>
       <c r="N3" s="3">
-        <v>0.03321496024727821</v>
+        <v>0.03975110873579979</v>
       </c>
       <c r="O3" s="3">
-        <v>0.03763607889413834</v>
+        <v>0.03829742595553398</v>
       </c>
       <c r="P3" s="3">
-        <v>0.03397868573665619</v>
+        <v>0.04252811893820763</v>
       </c>
       <c r="Q3" s="3">
-        <v>0.03543085604906082</v>
+        <v>0.02272970415651798</v>
       </c>
       <c r="R3" s="3">
-        <v>0.04314904287457466</v>
+        <v>0.04216959327459335</v>
       </c>
       <c r="S3" s="3">
-        <v>0.03326652944087982</v>
+        <v>0.03865154832601547</v>
       </c>
       <c r="T3" s="3">
-        <v>0.02961819060146809</v>
+        <v>0.0211221519857645</v>
       </c>
       <c r="U3" s="3">
-        <v>0.0338367186486721</v>
+        <v>0.02317719347774982</v>
       </c>
       <c r="V3" s="3">
-        <v>0.03251093626022339</v>
+        <v>0.03317374736070633</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0.02655530720949173</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0.01359112188220024</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>0.02304442413151264</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>0.02616900391876698</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>0.02320788614451885</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>0.02291245013475418</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>0.03490860760211945</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>0.02126434631645679</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>0.03014202602207661</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>0.03733185678720474</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>0.02669609896838665</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>0.03157204389572144</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>0.02713794261217117</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>0.0369231104850769</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>0.03736861050128937</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3">
-        <v>0.05954457074403763</v>
+        <v>0.05526045709848404</v>
       </c>
       <c r="D4" s="3">
-        <v>0.06433945149183273</v>
+        <v>0.04985054582357407</v>
       </c>
       <c r="E4" s="3">
-        <v>0.06205608323216438</v>
+        <v>0.03763815015554428</v>
       </c>
       <c r="F4" s="3">
-        <v>0.0643591433763504</v>
+        <v>0.05008355155587196</v>
       </c>
       <c r="G4" s="3">
-        <v>0.0663820132613182</v>
+        <v>0.04367544129490852</v>
       </c>
       <c r="H4" s="3">
-        <v>0.06086836010217667</v>
+        <v>0.04672465473413467</v>
       </c>
       <c r="I4" s="3">
-        <v>0.05980235710740089</v>
+        <v>0.05220967158675194</v>
       </c>
       <c r="J4" s="3">
-        <v>0.06305673718452454</v>
+        <v>0.06335801631212234</v>
       </c>
       <c r="K4" s="3">
-        <v>0.06502263993024826</v>
+        <v>0.06528415530920029</v>
       </c>
       <c r="L4" s="3">
-        <v>0.06575382500886917</v>
+        <v>0.05809431523084641</v>
       </c>
       <c r="M4" s="3">
-        <v>0.05604685097932816</v>
+        <v>0.06273824721574783</v>
       </c>
       <c r="N4" s="3">
-        <v>0.05593011528253555</v>
+        <v>0.06008524820208549</v>
       </c>
       <c r="O4" s="3">
-        <v>0.05680631846189499</v>
+        <v>0.06319522857666016</v>
       </c>
       <c r="P4" s="3">
-        <v>0.05591408908367157</v>
+        <v>0.05436429381370544</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.05968478322029114</v>
+        <v>0.0551144927740097</v>
       </c>
       <c r="R4" s="3">
-        <v>0.0649278312921524</v>
+        <v>0.05594957247376442</v>
       </c>
       <c r="S4" s="3">
-        <v>0.0681326761841774</v>
+        <v>0.05383197590708733</v>
       </c>
       <c r="T4" s="3">
-        <v>0.0540229007601738</v>
+        <v>0.03684019669890404</v>
       </c>
       <c r="U4" s="3">
-        <v>0.06899449229240417</v>
+        <v>0.03945264220237732</v>
       </c>
       <c r="V4" s="3">
-        <v>0.06295031309127808</v>
+        <v>0.0505010150372982</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.04268642887473106</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0.05878175795078278</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>0.05364882200956345</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>0.05027683451771736</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>0.05074167996644974</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0.04519708082079887</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0.06175806000828743</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0.04966536909341812</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>0.05127991735935211</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>0.05442365258932114</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>0.0511511042714119</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>0.05556081607937813</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>0.0498155914247036</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>0.0558263286948204</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>0.06054394692182541</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3">
-        <v>0.06751636415719986</v>
+        <v>0.03178394213318825</v>
       </c>
       <c r="D5" s="3">
-        <v>0.0734020471572876</v>
+        <v>0.05404948815703392</v>
       </c>
       <c r="E5" s="3">
-        <v>0.06425641477108002</v>
+        <v>0.04555796086788177</v>
       </c>
       <c r="F5" s="3">
-        <v>0.07239747047424316</v>
+        <v>0.05428257584571838</v>
       </c>
       <c r="G5" s="3">
-        <v>0.06476804614067078</v>
+        <v>0.04611386731266975</v>
       </c>
       <c r="H5" s="3">
-        <v>0.06859973818063736</v>
+        <v>0.04017078876495361</v>
       </c>
       <c r="I5" s="3">
-        <v>0.06489364057779312</v>
+        <v>0.05750171840190887</v>
       </c>
       <c r="J5" s="3">
-        <v>0.07607856392860413</v>
+        <v>0.06453313678503036</v>
       </c>
       <c r="K5" s="3">
-        <v>0.07952865213155746</v>
+        <v>0.0685720220208168</v>
       </c>
       <c r="L5" s="3">
-        <v>0.07965924590826035</v>
+        <v>0.05592713505029678</v>
       </c>
       <c r="M5" s="3">
-        <v>0.06982139497995377</v>
+        <v>0.06153701990842819</v>
       </c>
       <c r="N5" s="3">
-        <v>0.0720936506986618</v>
+        <v>0.057099848985672</v>
       </c>
       <c r="O5" s="3">
-        <v>0.07292982935905457</v>
+        <v>0.0579916425049305</v>
       </c>
       <c r="P5" s="3">
-        <v>0.06411031633615494</v>
+        <v>0.05054523795843124</v>
       </c>
       <c r="Q5" s="3">
-        <v>0.07580254971981049</v>
+        <v>0.04961604624986649</v>
       </c>
       <c r="R5" s="3">
-        <v>0.07193566113710403</v>
+        <v>0.06371581554412842</v>
       </c>
       <c r="S5" s="3">
-        <v>0.08319035172462463</v>
+        <v>0.05302393436431885</v>
       </c>
       <c r="T5" s="3">
-        <v>0.06679568439722061</v>
+        <v>0.02510764822363853</v>
       </c>
       <c r="U5" s="3">
-        <v>0.0729338526725769</v>
+        <v>0.03156422078609467</v>
       </c>
       <c r="V5" s="3">
-        <v>0.08092527836561203</v>
+        <v>0.04266836866736412</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0.03239244595170021</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0.03608560562133789</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>0.03463144600391388</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>0.03939558193087578</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>0.04363920167088509</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>0.02554132044315338</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>0.05061614513397217</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>0.04457473754882812</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>0.04739280790090561</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>0.06840642541646957</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>0.051097571849823</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>0.06568742543458939</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>0.0509328693151474</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>0.06955308467149734</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>0.06766228377819061</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3">
-        <v>0.01420033350586891</v>
+        <v>0.02181676402688026</v>
       </c>
       <c r="D6" s="3">
-        <v>0.02812691777944565</v>
+        <v>0.0231744758784771</v>
       </c>
       <c r="E6" s="3">
-        <v>0.02156144566833973</v>
+        <v>0.01093060337007046</v>
       </c>
       <c r="F6" s="3">
-        <v>0.02258316986262798</v>
+        <v>0.02156670950353146</v>
       </c>
       <c r="G6" s="3">
-        <v>0.02511370182037354</v>
+        <v>0.02430395036935806</v>
       </c>
       <c r="H6" s="3">
-        <v>0.01048105210065842</v>
+        <v>0.015565050765872</v>
       </c>
       <c r="I6" s="3">
-        <v>0.02770016901195049</v>
+        <v>0.02649029903113842</v>
       </c>
       <c r="J6" s="3">
-        <v>0.01996172219514847</v>
+        <v>0.03292368724942207</v>
       </c>
       <c r="K6" s="3">
-        <v>0.02169737964868546</v>
+        <v>0.04164626449346542</v>
       </c>
       <c r="L6" s="3">
-        <v>0.02344574779272079</v>
+        <v>0.02915762178599834</v>
       </c>
       <c r="M6" s="3">
-        <v>0.01802794449031353</v>
+        <v>0.0366266705095768</v>
       </c>
       <c r="N6" s="3">
-        <v>0.02598590962588787</v>
+        <v>0.03276323154568672</v>
       </c>
       <c r="O6" s="3">
-        <v>0.02476801350712776</v>
+        <v>0.03267916664481163</v>
       </c>
       <c r="P6" s="3">
-        <v>0.02367888949811459</v>
+        <v>0.03737932443618774</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.02756121568381786</v>
+        <v>0.02527002245187759</v>
       </c>
       <c r="R6" s="3">
-        <v>0.0231388732790947</v>
+        <v>0.0425698347389698</v>
       </c>
       <c r="S6" s="3">
-        <v>0.02089239656925201</v>
+        <v>0.03593906387686729</v>
       </c>
       <c r="T6" s="3">
-        <v>0.02248717099428177</v>
+        <v>0.01351193618029356</v>
       </c>
       <c r="U6" s="3">
-        <v>0.02774855121970177</v>
+        <v>0.01482726540416479</v>
       </c>
       <c r="V6" s="3">
-        <v>0.03569304943084717</v>
+        <v>0.02975256554782391</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0.02255265042185783</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0.02632226794958115</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>0.0277574323117733</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>0.02409759722650051</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>0.02336724475026131</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0.01787721365690231</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>0.03394635766744614</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0.02202458307147026</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>0.03422886505723</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0.04686976224184036</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>0.03680642321705818</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>0.03875584527850151</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>0.03110635653138161</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>0.04374600574374199</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>0.04421026632189751</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3">
-        <v>0.08337989449501038</v>
+        <v>0.05324559286236763</v>
       </c>
       <c r="D7" s="3">
-        <v>0.08247369527816772</v>
+        <v>0.07137318700551987</v>
       </c>
       <c r="E7" s="3">
-        <v>0.08287862688302994</v>
+        <v>0.05850685015320778</v>
       </c>
       <c r="F7" s="3">
-        <v>0.08650974184274673</v>
+        <v>0.07098938524723053</v>
       </c>
       <c r="G7" s="3">
-        <v>0.0817936509847641</v>
+        <v>0.0638490542769432</v>
       </c>
       <c r="H7" s="3">
-        <v>0.06720809638500214</v>
+        <v>0.06784535944461823</v>
       </c>
       <c r="I7" s="3">
-        <v>0.05112197622656822</v>
+        <v>0.07421273738145828</v>
       </c>
       <c r="J7" s="3">
-        <v>0.07861657440662384</v>
+        <v>0.07403621077537537</v>
       </c>
       <c r="K7" s="3">
-        <v>0.08327347040176392</v>
+        <v>0.08997694402933121</v>
       </c>
       <c r="L7" s="3">
-        <v>0.07554458826780319</v>
+        <v>0.08497940003871918</v>
       </c>
       <c r="M7" s="3">
-        <v>0.08451878279447556</v>
+        <v>0.08338512480258942</v>
       </c>
       <c r="N7" s="3">
-        <v>0.07777140289545059</v>
+        <v>0.08324588090181351</v>
       </c>
       <c r="O7" s="3">
-        <v>0.08891043066978455</v>
+        <v>0.08055596053600311</v>
       </c>
       <c r="P7" s="3">
-        <v>0.08953049033880234</v>
+        <v>0.07379558682441711</v>
       </c>
       <c r="Q7" s="3">
-        <v>0.08629905432462692</v>
+        <v>0.07139824330806732</v>
       </c>
       <c r="R7" s="3">
-        <v>0.0851573646068573</v>
+        <v>0.09145644307136536</v>
       </c>
       <c r="S7" s="3">
-        <v>0.08062366396188736</v>
+        <v>0.08142636716365814</v>
       </c>
       <c r="T7" s="3">
-        <v>0.08195805549621582</v>
+        <v>0.06458508968353271</v>
       </c>
       <c r="U7" s="3">
-        <v>0.07549872249364853</v>
+        <v>0.06795041263103485</v>
       </c>
       <c r="V7" s="3">
-        <v>0.07724808901548386</v>
+        <v>0.07891494035720825</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0.07438270002603531</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0.03842853009700775</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>0.0714416354894638</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>0.06691300868988037</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>0.06721946597099304</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>0.05433462560176849</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>0.08129431307315826</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0.0663154274225235</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>0.07287239283323288</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>0.08276666700839996</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>0.07429676502943039</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>0.07953540235757828</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0.07907092571258545</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>0.07793404906988144</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>0.08641185611486435</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C8" s="3">
-        <v>0.07976994663476944</v>
+        <v>0.05214964970946312</v>
       </c>
       <c r="D8" s="3">
-        <v>0.09327749907970428</v>
+        <v>0.06493152678012848</v>
       </c>
       <c r="E8" s="3">
-        <v>0.08455102890729904</v>
+        <v>0.05406946316361427</v>
       </c>
       <c r="F8" s="3">
-        <v>0.08995547145605087</v>
+        <v>0.06670589745044708</v>
       </c>
       <c r="G8" s="3">
-        <v>0.08181437104940414</v>
+        <v>0.05982556939125061</v>
       </c>
       <c r="H8" s="3">
-        <v>0.06108132377266884</v>
+        <v>0.06161116436123848</v>
       </c>
       <c r="I8" s="3">
-        <v>0.06955923140048981</v>
+        <v>0.06944037973880768</v>
       </c>
       <c r="J8" s="3">
-        <v>0.06871117651462555</v>
+        <v>0.07365690916776657</v>
       </c>
       <c r="K8" s="3">
-        <v>0.06785769015550613</v>
+        <v>0.07726751267910004</v>
       </c>
       <c r="L8" s="3">
-        <v>0.07060565799474716</v>
+        <v>0.07197146117687225</v>
       </c>
       <c r="M8" s="3">
-        <v>0.06164061278104782</v>
+        <v>0.07519146800041199</v>
       </c>
       <c r="N8" s="3">
-        <v>0.06781958788633347</v>
+        <v>0.07480188459157944</v>
       </c>
       <c r="O8" s="3">
-        <v>0.06714211404323578</v>
+        <v>0.06830517947673798</v>
       </c>
       <c r="P8" s="3">
-        <v>0.05917524546384811</v>
+        <v>0.07700598984956741</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.06806494295597076</v>
+        <v>0.06499364972114563</v>
       </c>
       <c r="R8" s="3">
-        <v>0.09078509360551834</v>
+        <v>0.07791602611541748</v>
       </c>
       <c r="S8" s="3">
-        <v>0.06897357106208801</v>
+        <v>0.06705628335475922</v>
       </c>
       <c r="T8" s="3">
-        <v>0.06557249277830124</v>
+        <v>0.05031842365860939</v>
       </c>
       <c r="U8" s="3">
-        <v>0.0731942430138588</v>
+        <v>0.05484896153211594</v>
       </c>
       <c r="V8" s="3">
-        <v>0.07428449392318726</v>
+        <v>0.05599984526634216</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0.05870629101991653</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0.04348962754011154</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0.05431738123297691</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0.05186733603477478</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0.05967414006590843</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0.04965187236666679</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0.0632118433713913</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0.05601679906249046</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0.05134190618991852</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0.07248997688293457</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0.05847804248332977</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0.06833868473768234</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0.06086035072803497</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>0.06817716360092163</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>0.07234404981136322</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3">
-        <v>0.05308482423424721</v>
+        <v>0.03064927831292152</v>
       </c>
       <c r="D9" s="3">
-        <v>0.066020667552948</v>
+        <v>0.03957038372755051</v>
       </c>
       <c r="E9" s="3">
-        <v>0.06564678996801376</v>
+        <v>0.02795966900885105</v>
       </c>
       <c r="F9" s="3">
-        <v>0.06083356589078903</v>
+        <v>0.04231652989983559</v>
       </c>
       <c r="G9" s="3">
-        <v>0.06143420189619064</v>
+        <v>0.03983583301305771</v>
       </c>
       <c r="H9" s="3">
-        <v>0.04652511700987816</v>
+        <v>0.03180885314941406</v>
       </c>
       <c r="I9" s="3">
-        <v>0.03684128448367119</v>
+        <v>0.04499394074082375</v>
       </c>
       <c r="J9" s="3">
-        <v>0.06566676497459412</v>
+        <v>0.05198594555258751</v>
       </c>
       <c r="K9" s="3">
-        <v>0.06749401986598969</v>
+        <v>0.0627630203962326</v>
       </c>
       <c r="L9" s="3">
-        <v>0.06637317687273026</v>
+        <v>0.05384038761258125</v>
       </c>
       <c r="M9" s="3">
-        <v>0.04759922251105309</v>
+        <v>0.05907192081212997</v>
       </c>
       <c r="N9" s="3">
-        <v>0.05016208440065384</v>
+        <v>0.05739066749811172</v>
       </c>
       <c r="O9" s="3">
-        <v>0.05959214642643929</v>
+        <v>0.05461475998163223</v>
       </c>
       <c r="P9" s="3">
-        <v>0.05425899103283882</v>
+        <v>0.05630828812718391</v>
       </c>
       <c r="Q9" s="3">
-        <v>0.06161560863256454</v>
+        <v>0.04223765060305595</v>
       </c>
       <c r="R9" s="3">
-        <v>0.06547313928604126</v>
+        <v>0.05622314661741257</v>
       </c>
       <c r="S9" s="3">
-        <v>0.06543613225221634</v>
+        <v>0.0531502291560173</v>
       </c>
       <c r="T9" s="3">
-        <v>0.05513908714056015</v>
+        <v>0.02802661061286926</v>
       </c>
       <c r="U9" s="3">
-        <v>0.05830733105540276</v>
+        <v>0.03184995055198669</v>
       </c>
       <c r="V9" s="3">
-        <v>0.06137459725141525</v>
+        <v>0.04064851626753807</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0.0376608744263649</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0.02740795910358429</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>0.03018738888204098</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>0.03853706270456314</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>0.03828472644090652</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>0.02837255969643593</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>0.04805171862244606</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>0.03692908212542534</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>0.04485896974802017</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0.05659652128815651</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>0.04183243960142136</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>0.05185472220182419</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0.04617857560515404</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>0.05657757818698883</v>
+      </c>
+      <c r="AK9" s="3">
+        <v>0.05724514275789261</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3">
-        <v>0.09308630228042603</v>
+        <v>0.07364946603775024</v>
       </c>
       <c r="D10" s="3">
-        <v>0.09417959302663803</v>
+        <v>0.05811735615134239</v>
       </c>
       <c r="E10" s="3">
-        <v>0.08316748589277267</v>
+        <v>0.04982313141226768</v>
       </c>
       <c r="F10" s="3">
-        <v>0.08641235530376434</v>
+        <v>0.05448940768837929</v>
       </c>
       <c r="G10" s="3">
-        <v>0.08945445716381073</v>
+        <v>0.0620860829949379</v>
       </c>
       <c r="H10" s="3">
-        <v>0.06201968342065811</v>
+        <v>0.05576618015766144</v>
       </c>
       <c r="I10" s="3">
-        <v>0.05532891675829887</v>
+        <v>0.06019524112343788</v>
       </c>
       <c r="J10" s="3">
-        <v>0.0632651075720787</v>
+        <v>0.0701831579208374</v>
       </c>
       <c r="K10" s="3">
-        <v>0.06577792763710022</v>
+        <v>0.0531848706305027</v>
       </c>
       <c r="L10" s="3">
-        <v>0.0654376670718193</v>
+        <v>0.04771455004811287</v>
       </c>
       <c r="M10" s="3">
-        <v>0.06333690136671066</v>
+        <v>0.04881846532225609</v>
       </c>
       <c r="N10" s="3">
-        <v>0.05763601139187813</v>
+        <v>0.0510738417506218</v>
       </c>
       <c r="O10" s="3">
-        <v>0.06207523494958878</v>
+        <v>0.05614545941352844</v>
       </c>
       <c r="P10" s="3">
-        <v>0.05953468754887581</v>
+        <v>0.05328124016523361</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.0548095591366291</v>
+        <v>0.06303853541612625</v>
       </c>
       <c r="R10" s="3">
-        <v>0.08364900201559067</v>
+        <v>0.06503599882125854</v>
       </c>
       <c r="S10" s="3">
-        <v>0.05883291736245155</v>
+        <v>0.0638182982802391</v>
       </c>
       <c r="T10" s="3">
-        <v>0.05082724243402481</v>
+        <v>0.03624235466122627</v>
       </c>
       <c r="U10" s="3">
-        <v>0.05299947783350945</v>
+        <v>0.04387087002396584</v>
       </c>
       <c r="V10" s="3">
-        <v>0.05667315796017647</v>
+        <v>0.05245595425367355</v>
+      </c>
+      <c r="W10" s="3">
+        <v>0.04077962413430214</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0.05063160136342049</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>0.05139575153589249</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0.04898509383201599</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0.0436592735350132</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0.03916792944073677</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0.06155378744006157</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0.04205890744924545</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0.04937874525785446</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0.06839734315872192</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0.06274643540382385</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0.06365004181861877</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0.06800070405006409</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>0.06259558349847794</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>0.06632675975561142</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3">
-        <v>0.06096208840608597</v>
+        <v>0.03629170358181</v>
       </c>
       <c r="D11" s="3">
-        <v>0.06017793715000153</v>
+        <v>0.04105052724480629</v>
       </c>
       <c r="E11" s="3">
-        <v>0.06369195878505707</v>
+        <v>0.02757998369634151</v>
       </c>
       <c r="F11" s="3">
-        <v>0.06416578590869904</v>
+        <v>0.03691205382347107</v>
       </c>
       <c r="G11" s="3">
-        <v>0.056578129529953</v>
+        <v>0.03522539138793945</v>
       </c>
       <c r="H11" s="3">
-        <v>0.05408993735909462</v>
+        <v>0.03198732808232307</v>
       </c>
       <c r="I11" s="3">
-        <v>0.001088871620595455</v>
+        <v>0.04356134310364723</v>
       </c>
       <c r="J11" s="3">
-        <v>0.05698569864034653</v>
+        <v>0.04939249902963638</v>
       </c>
       <c r="K11" s="3">
-        <v>0.05225089564919472</v>
+        <v>0.06367932260036469</v>
       </c>
       <c r="L11" s="3">
-        <v>0.06008931621909142</v>
+        <v>0.05373908206820488</v>
       </c>
       <c r="M11" s="3">
-        <v>0.04809422045946121</v>
+        <v>0.06043045595288277</v>
       </c>
       <c r="N11" s="3">
-        <v>0.02669769898056984</v>
+        <v>0.05784635990858078</v>
       </c>
       <c r="O11" s="3">
-        <v>0.05291163176298141</v>
+        <v>0.04514884948730469</v>
       </c>
       <c r="P11" s="3">
-        <v>0.04022336006164551</v>
+        <v>0.0640529915690422</v>
       </c>
       <c r="Q11" s="3">
-        <v>0.04823961853981018</v>
+        <v>0.03809666633605957</v>
       </c>
       <c r="R11" s="3">
-        <v>0.07255655527114868</v>
+        <v>0.05080255120992661</v>
       </c>
       <c r="S11" s="3">
-        <v>0.05906013026833534</v>
+        <v>0.05021970719099045</v>
       </c>
       <c r="T11" s="3">
-        <v>0.05217373743653297</v>
+        <v>0.02790032140910625</v>
       </c>
       <c r="U11" s="3">
-        <v>0.05406501889228821</v>
+        <v>0.0272735059261322</v>
       </c>
       <c r="V11" s="3">
-        <v>0.04591966420412064</v>
+        <v>0.027283089235425</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0.03246639668941498</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0.0231911726295948</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0.03070732392370701</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>0.03351080417633057</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>0.03150960430502892</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>0.02418286167085171</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>0.03723898157477379</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0.03272167593240738</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>0.04801045358181</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0.05969063565135002</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0.0413784570991993</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>0.05225610733032227</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>0.04778251051902771</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>0.04876281693577766</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>0.06002507358789444</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
-        <v>0.06104457378387451</v>
+        <v>0.05164365842938423</v>
       </c>
       <c r="D12" s="3">
-        <v>0.06946956366300583</v>
+        <v>0.0307910330593586</v>
       </c>
       <c r="E12" s="3">
-        <v>0.05185747146606445</v>
+        <v>0.01356085203588009</v>
       </c>
       <c r="F12" s="3">
-        <v>0.05534955114126205</v>
+        <v>0.02743876352906227</v>
       </c>
       <c r="G12" s="3">
-        <v>0.05928869172930717</v>
+        <v>0.02145982533693314</v>
       </c>
       <c r="H12" s="3">
-        <v>0.04568466916680336</v>
+        <v>0.02068719267845154</v>
       </c>
       <c r="I12" s="3">
-        <v>0.04312038794159889</v>
+        <v>0.03176125511527061</v>
       </c>
       <c r="J12" s="3">
-        <v>0.04494937509298325</v>
+        <v>0.05167143419384956</v>
       </c>
       <c r="K12" s="3">
-        <v>0.04138793051242828</v>
+        <v>0.05391381680965424</v>
       </c>
       <c r="L12" s="3">
-        <v>0.04734392464160919</v>
+        <v>0.03401309251785278</v>
       </c>
       <c r="M12" s="3">
-        <v>0.04863834008574486</v>
+        <v>0.04652437195181847</v>
       </c>
       <c r="N12" s="3">
-        <v>0.04805511608719826</v>
+        <v>0.04709431156516075</v>
       </c>
       <c r="O12" s="3">
-        <v>0.0427062138915062</v>
+        <v>0.03766303882002831</v>
       </c>
       <c r="P12" s="3">
-        <v>0.03104057535529137</v>
+        <v>0.04660267382860184</v>
       </c>
       <c r="Q12" s="3">
-        <v>0.04203302040696144</v>
+        <v>0.03540726378560066</v>
       </c>
       <c r="R12" s="3">
-        <v>0.0550532229244709</v>
+        <v>0.04900509864091873</v>
       </c>
       <c r="S12" s="3">
-        <v>0.040070541203022</v>
+        <v>0.04394439607858658</v>
       </c>
       <c r="T12" s="3">
-        <v>0.04089532792568207</v>
+        <v>0.01767316088080406</v>
       </c>
       <c r="U12" s="3">
-        <v>0.02592014335095882</v>
+        <v>0.02550816722214222</v>
       </c>
       <c r="V12" s="3">
-        <v>0.04278457909822464</v>
+        <v>0.02239899709820747</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0.02687916532158852</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0.02416565828025341</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>0.02208901196718216</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>0.02094093710184097</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0.02493298053741455</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0.01853504963219166</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>0.02588835544884205</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0.02408450096845627</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>0.04340709745883942</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0.05518123880028725</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>0.04175715148448944</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>0.04691521823406219</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>0.0459870807826519</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>0.05123313516378403</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>0.05148511007428169</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3">
-        <v>0.06686469167470932</v>
+        <v>0.058656245470047</v>
       </c>
       <c r="D13" s="3">
-        <v>0.07542363554239273</v>
+        <v>0.05464575812220573</v>
       </c>
       <c r="E13" s="3">
-        <v>0.05889124423265457</v>
+        <v>0.04264084249734879</v>
       </c>
       <c r="F13" s="3">
-        <v>0.06660234928131104</v>
+        <v>0.05232648178935051</v>
       </c>
       <c r="G13" s="3">
-        <v>0.0656697154045105</v>
+        <v>0.06053201854228973</v>
       </c>
       <c r="H13" s="3">
-        <v>0.04379582032561302</v>
+        <v>0.04528233781456947</v>
       </c>
       <c r="I13" s="3">
-        <v>0.03236864134669304</v>
+        <v>0.05747385323047638</v>
       </c>
       <c r="J13" s="3">
-        <v>0.05258876085281372</v>
+        <v>0.0776640772819519</v>
       </c>
       <c r="K13" s="3">
-        <v>0.05062052235007286</v>
+        <v>0.07394026219844818</v>
       </c>
       <c r="L13" s="3">
-        <v>0.05190237239003181</v>
+        <v>0.05880047380924225</v>
       </c>
       <c r="M13" s="3">
-        <v>0.0499914288520813</v>
+        <v>0.060708899050951</v>
       </c>
       <c r="N13" s="3">
-        <v>0.05058707296848297</v>
+        <v>0.06157468631863594</v>
       </c>
       <c r="O13" s="3">
-        <v>0.05358045548200607</v>
+        <v>0.05401474237442017</v>
       </c>
       <c r="P13" s="3">
-        <v>0.04349973425269127</v>
+        <v>0.04825418815016747</v>
       </c>
       <c r="Q13" s="3">
-        <v>0.05253620073199272</v>
+        <v>0.06241417303681374</v>
       </c>
       <c r="R13" s="3">
-        <v>0.06896932423114777</v>
+        <v>0.07543088495731354</v>
       </c>
       <c r="S13" s="3">
-        <v>0.05590881407260895</v>
+        <v>0.07174623012542725</v>
       </c>
       <c r="T13" s="3">
-        <v>0.05165264755487442</v>
+        <v>0.03724019229412079</v>
       </c>
       <c r="U13" s="3">
-        <v>0.05333168804645538</v>
+        <v>0.05049760267138481</v>
       </c>
       <c r="V13" s="3">
-        <v>0.05021675676107407</v>
+        <v>0.0479373000562191</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.04455119371414185</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.04919079691171646</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0.04439810290932655</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0.03994759544730186</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0.04258764535188675</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0.04335625842213631</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0.05952993407845497</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0.03933265060186386</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0.05488981306552887</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0.07745648920536041</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0.0536927655339241</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0.06187007576227188</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0.0579172819852829</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0.0691460371017456</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0.06672412157058716</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3">
-        <v>0.05385226756334305</v>
+        <v>0.0512639582157135</v>
       </c>
       <c r="D14" s="3">
-        <v>0.05167323723435402</v>
+        <v>0.04974993318319321</v>
       </c>
       <c r="E14" s="3">
-        <v>0.05205921456217766</v>
+        <v>0.03865119814872742</v>
       </c>
       <c r="F14" s="3">
-        <v>0.05332290753722191</v>
+        <v>0.04811500757932663</v>
       </c>
       <c r="G14" s="3">
-        <v>0.05448191985487938</v>
+        <v>0.04878843575716019</v>
       </c>
       <c r="H14" s="3">
-        <v>0.05113320797681808</v>
+        <v>0.03827222064137459</v>
       </c>
       <c r="I14" s="3">
-        <v>0.04753010720014572</v>
+        <v>0.05167516320943832</v>
       </c>
       <c r="J14" s="3">
-        <v>0.05529792606830597</v>
+        <v>0.07035724818706512</v>
       </c>
       <c r="K14" s="3">
-        <v>0.05397718772292137</v>
+        <v>0.069584921002388</v>
       </c>
       <c r="L14" s="3">
-        <v>0.05688647925853729</v>
+        <v>0.06680348515510559</v>
       </c>
       <c r="M14" s="3">
-        <v>0.04953981190919876</v>
+        <v>0.06742560118436813</v>
       </c>
       <c r="N14" s="3">
-        <v>0.04269054532051086</v>
+        <v>0.06794428080320358</v>
       </c>
       <c r="O14" s="3">
-        <v>0.05161000788211823</v>
+        <v>0.05821237713098526</v>
       </c>
       <c r="P14" s="3">
-        <v>0.0453033372759819</v>
+        <v>0.06189499795436859</v>
       </c>
       <c r="Q14" s="3">
-        <v>0.05093438178300858</v>
+        <v>0.05779270082712173</v>
       </c>
       <c r="R14" s="3">
-        <v>0.05416825413703918</v>
+        <v>0.0741538479924202</v>
       </c>
       <c r="S14" s="3">
-        <v>0.05510084331035614</v>
+        <v>0.06476227939128876</v>
       </c>
       <c r="T14" s="3">
-        <v>0.04482584819197655</v>
+        <v>0.04747910052537918</v>
       </c>
       <c r="U14" s="3">
-        <v>0.05684532970190048</v>
+        <v>0.05477340519428253</v>
       </c>
       <c r="V14" s="3">
-        <v>0.04931098595261574</v>
+        <v>0.05325287953019142</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0.05049044638872147</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0.05431025102734566</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0.05800554901361465</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0.05392074212431908</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0.05520477145910263</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0.05513143539428711</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0.06081137806177139</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0.0522603765130043</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0.04845098406076431</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0.05865570530295372</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0.04624541103839874</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0.04986250028014183</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0.04460282251238823</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0.05387827008962631</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0.05684517323970795</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C15" s="3">
-        <v>0.03155335411429405</v>
+        <v>0.02008962072432041</v>
       </c>
       <c r="D15" s="3">
-        <v>0.03623712435364723</v>
+        <v>0.02026350051164627</v>
       </c>
       <c r="E15" s="3">
-        <v>0.03427321836352348</v>
+        <v>0.00990307703614235</v>
       </c>
       <c r="F15" s="3">
-        <v>0.03937828540802002</v>
+        <v>0.01962198689579964</v>
       </c>
       <c r="G15" s="3">
-        <v>0.03139786422252655</v>
+        <v>0.01963097602128983</v>
       </c>
       <c r="H15" s="3">
-        <v>0.01597430557012558</v>
+        <v>0.02581115439534187</v>
       </c>
       <c r="I15" s="3">
-        <v>0.01541309431195259</v>
+        <v>0.02329371683299541</v>
       </c>
       <c r="J15" s="3">
-        <v>0.02141163684427738</v>
+        <v>0.02468843385577202</v>
       </c>
       <c r="K15" s="3">
-        <v>0.02607862465083599</v>
+        <v>0.02225592359900475</v>
       </c>
       <c r="L15" s="3">
-        <v>0.02481912262737751</v>
+        <v>0.01634396240115166</v>
       </c>
       <c r="M15" s="3">
-        <v>0.01779764890670776</v>
+        <v>0.01659786514937878</v>
       </c>
       <c r="N15" s="3">
-        <v>0.02069328911602497</v>
+        <v>0.01693209260702133</v>
       </c>
       <c r="O15" s="3">
-        <v>0.02471863850951195</v>
+        <v>0.02289685793220997</v>
       </c>
       <c r="P15" s="3">
-        <v>0.02144166268408298</v>
+        <v>0.01797031983733177</v>
       </c>
       <c r="Q15" s="3">
-        <v>0.02583137154579163</v>
+        <v>0.03044828958809376</v>
       </c>
       <c r="R15" s="3">
-        <v>0.0400603711605072</v>
+        <v>0.02794645726680756</v>
       </c>
       <c r="S15" s="3">
-        <v>0.02349554188549519</v>
+        <v>0.02922678738832474</v>
       </c>
       <c r="T15" s="3">
-        <v>0.02143916301429272</v>
+        <v>0.005412752740085125</v>
       </c>
       <c r="U15" s="3">
-        <v>0.02106420323252678</v>
+        <v>0.01040556374937296</v>
       </c>
       <c r="V15" s="3">
-        <v>0.0254353154450655</v>
+        <v>0.02581774815917015</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0.01231883745640516</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0.004564174450933933</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>-0.003598806215450168</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0.004863649141043425</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0.0003084027557633817</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>-0.002923921681940556</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0.02186540141701698</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0.001752827083691955</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0.0263838991522789</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0.03247879818081856</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0.0255354717373848</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0.02966051176190376</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0.02963127568364143</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>0.03851158171892166</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0.03212789073586464</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C16" s="3">
-        <v>0.07975427806377411</v>
+        <v>0.03408128768205643</v>
       </c>
       <c r="D16" s="3">
-        <v>0.07756397128105164</v>
+        <v>0.05557620152831078</v>
       </c>
       <c r="E16" s="3">
-        <v>0.06677163392305374</v>
+        <v>0.05271391198039055</v>
       </c>
       <c r="F16" s="3">
-        <v>0.07898380607366562</v>
+        <v>0.05604636669158936</v>
       </c>
       <c r="G16" s="3">
-        <v>0.08312813192605972</v>
+        <v>0.06043796986341476</v>
       </c>
       <c r="H16" s="3">
-        <v>0.07025404274463654</v>
+        <v>0.0585097000002861</v>
       </c>
       <c r="I16" s="3">
-        <v>0.08538946509361267</v>
+        <v>0.0599457174539566</v>
       </c>
       <c r="J16" s="3">
-        <v>0.05985688045620918</v>
+        <v>0.03331901133060455</v>
       </c>
       <c r="K16" s="3">
-        <v>0.06509898602962494</v>
+        <v>0.05138595774769783</v>
       </c>
       <c r="L16" s="3">
-        <v>0.0624602846801281</v>
+        <v>0.04604818299412727</v>
       </c>
       <c r="M16" s="3">
-        <v>0.05794476345181465</v>
+        <v>0.05127698928117752</v>
       </c>
       <c r="N16" s="3">
-        <v>0.05527937039732933</v>
+        <v>0.05380195379257202</v>
       </c>
       <c r="O16" s="3">
-        <v>0.0497807152569294</v>
+        <v>0.05862260609865189</v>
       </c>
       <c r="P16" s="3">
-        <v>0.04806318506598473</v>
+        <v>0.04685128480195999</v>
       </c>
       <c r="Q16" s="3">
-        <v>0.04229233413934708</v>
+        <v>0.03475649654865265</v>
       </c>
       <c r="R16" s="3">
-        <v>0.0709829106926918</v>
+        <v>0.05704739689826965</v>
       </c>
       <c r="S16" s="3">
-        <v>0.05566330626606941</v>
+        <v>0.04518899321556091</v>
       </c>
       <c r="T16" s="3">
-        <v>0.04556579887866974</v>
+        <v>0.03238718211650848</v>
       </c>
       <c r="U16" s="3">
-        <v>0.05156505852937698</v>
+        <v>0.03812152519822121</v>
       </c>
       <c r="V16" s="3">
-        <v>0.06482962518930435</v>
+        <v>0.04376119002699852</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0.03158331662416458</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0.02570252120494843</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>0.0337192639708519</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0.0274979081004858</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>0.02934123389422894</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>0.02277438156306744</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>0.04259389638900757</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>0.02663182839751244</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>0.04393064603209496</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>0.05548570677638054</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>0.04836156964302063</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>0.05694839358329773</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>0.05293252691626549</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>0.05424783006310463</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>0.05596565827727318</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C17" s="3">
-        <v>0.06920979171991348</v>
+        <v>0.05186367034912109</v>
       </c>
       <c r="D17" s="3">
-        <v>0.0790102407336235</v>
+        <v>0.03717784956097603</v>
       </c>
       <c r="E17" s="3">
-        <v>0.06463015824556351</v>
+        <v>0.02969130873680115</v>
       </c>
       <c r="F17" s="3">
-        <v>0.07496556639671326</v>
+        <v>0.03854021802544594</v>
       </c>
       <c r="G17" s="3">
-        <v>0.05999541655182838</v>
+        <v>0.04445231705904007</v>
       </c>
       <c r="H17" s="3">
-        <v>0.04869742691516876</v>
+        <v>0.03931631147861481</v>
       </c>
       <c r="I17" s="3">
-        <v>0.04890339076519012</v>
+        <v>0.04174453392624855</v>
       </c>
       <c r="J17" s="3">
-        <v>0.05265884101390839</v>
+        <v>0.04344815015792847</v>
       </c>
       <c r="K17" s="3">
-        <v>0.05508560687303543</v>
+        <v>0.04610222950577736</v>
       </c>
       <c r="L17" s="3">
-        <v>0.05506286770105362</v>
+        <v>0.04243208467960358</v>
       </c>
       <c r="M17" s="3">
-        <v>0.04790861159563065</v>
+        <v>0.04258799180388451</v>
       </c>
       <c r="N17" s="3">
-        <v>0.04800072312355042</v>
+        <v>0.04544912278652191</v>
       </c>
       <c r="O17" s="3">
-        <v>0.05368302762508392</v>
+        <v>0.04014948010444641</v>
       </c>
       <c r="P17" s="3">
-        <v>0.04893819615244865</v>
+        <v>0.04520073160529137</v>
       </c>
       <c r="Q17" s="3">
-        <v>0.0480949841439724</v>
+        <v>0.04217036813497543</v>
       </c>
       <c r="R17" s="3">
-        <v>0.06809216737747192</v>
+        <v>0.05529799312353134</v>
       </c>
       <c r="S17" s="3">
-        <v>0.04789662733674049</v>
+        <v>0.04811709001660347</v>
       </c>
       <c r="T17" s="3">
-        <v>0.0450904592871666</v>
+        <v>0.02293866872787476</v>
       </c>
       <c r="U17" s="3">
-        <v>0.04067123308777809</v>
+        <v>0.03623020648956299</v>
       </c>
       <c r="V17" s="3">
-        <v>0.04117587581276894</v>
+        <v>0.0320575125515461</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0.02941050752997398</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.02271884493529797</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.02878981456160545</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0.0241303201764822</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0.02904261648654938</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>0.02781708166003227</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>0.03734098374843597</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>0.02431229501962662</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>0.0275740809738636</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>0.05102017521858215</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0.03476989641785622</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>0.04042608290910721</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>0.04573233053088188</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>0.03947445750236511</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>0.04506943747401237</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3">
-        <v>0.04177848622202873</v>
+        <v>0.01157102640718222</v>
       </c>
       <c r="D18" s="3">
-        <v>0.05967671424150467</v>
+        <v>0.03050024248659611</v>
       </c>
       <c r="E18" s="3">
-        <v>0.04470879584550858</v>
+        <v>0.01388960517942905</v>
       </c>
       <c r="F18" s="3">
-        <v>0.05017072707414627</v>
+        <v>0.03040645830333233</v>
       </c>
       <c r="G18" s="3">
-        <v>0.04308680444955826</v>
+        <v>0.02706054598093033</v>
       </c>
       <c r="H18" s="3">
-        <v>0.02305839210748672</v>
+        <v>0.02459935285151005</v>
       </c>
       <c r="I18" s="3">
-        <v>0.03047473356127739</v>
+        <v>0.03523673862218857</v>
       </c>
       <c r="J18" s="3">
-        <v>0.03336871415376663</v>
+        <v>0.03259322047233582</v>
       </c>
       <c r="K18" s="3">
-        <v>0.03661821782588959</v>
+        <v>0.05106465518474579</v>
       </c>
       <c r="L18" s="3">
-        <v>0.03215304017066956</v>
+        <v>0.03274250775575638</v>
       </c>
       <c r="M18" s="3">
-        <v>0.03481548279523849</v>
+        <v>0.0433436706662178</v>
       </c>
       <c r="N18" s="3">
-        <v>0.04326805472373962</v>
+        <v>0.04375597089529037</v>
       </c>
       <c r="O18" s="3">
-        <v>0.04195058345794678</v>
+        <v>0.03991319239139557</v>
       </c>
       <c r="P18" s="3">
-        <v>0.04310044646263123</v>
+        <v>0.03917430341243744</v>
       </c>
       <c r="Q18" s="3">
-        <v>0.03936272859573364</v>
+        <v>0.04522158950567245</v>
       </c>
       <c r="R18" s="3">
-        <v>0.05109609663486481</v>
+        <v>0.0640125572681427</v>
       </c>
       <c r="S18" s="3">
-        <v>0.03350841253995895</v>
+        <v>0.05502080544829369</v>
       </c>
       <c r="T18" s="3">
-        <v>0.0389903336763382</v>
+        <v>0.03150223940610886</v>
       </c>
       <c r="U18" s="3">
-        <v>0.0372370071709156</v>
+        <v>0.03693176060914993</v>
       </c>
       <c r="V18" s="3">
-        <v>0.03438008576631546</v>
+        <v>0.0387846864759922</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0.03971933200955391</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0.001852372195571661</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0.03126436099410057</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0.0178975984454155</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0.02526423335075378</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0.01214652322232723</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>0.03704403340816498</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0.0264013335108757</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>0.02609902061522007</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0.05077231675386429</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0.02657407708466053</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0.03802934288978577</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0.02995828166604042</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>0.04307923838496208</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>0.04674283042550087</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3">
-        <v>0.07092297822237015</v>
+        <v>0.05198002979159355</v>
       </c>
       <c r="D19" s="3">
-        <v>0.0868445411324501</v>
+        <v>0.0573156476020813</v>
       </c>
       <c r="E19" s="3">
-        <v>0.07645963877439499</v>
+        <v>0.05165074020624161</v>
       </c>
       <c r="F19" s="3">
-        <v>0.08003637939691544</v>
+        <v>0.05795543640851974</v>
       </c>
       <c r="G19" s="3">
-        <v>0.0817667692899704</v>
+        <v>0.05919907987117767</v>
       </c>
       <c r="H19" s="3">
-        <v>0.04302956908941269</v>
+        <v>0.05787042528390884</v>
       </c>
       <c r="I19" s="3">
-        <v>0.05554695427417755</v>
+        <v>0.06132446229457855</v>
       </c>
       <c r="J19" s="3">
-        <v>0.05321311578154564</v>
+        <v>0.05709630995988846</v>
       </c>
       <c r="K19" s="3">
-        <v>0.05269081518054008</v>
+        <v>0.05853568762540817</v>
       </c>
       <c r="L19" s="3">
-        <v>0.05389560014009476</v>
+        <v>0.05754422396421432</v>
       </c>
       <c r="M19" s="3">
-        <v>0.05189412087202072</v>
+        <v>0.05619553849101067</v>
       </c>
       <c r="N19" s="3">
-        <v>0.05814485996961594</v>
+        <v>0.05632463097572327</v>
       </c>
       <c r="O19" s="3">
-        <v>0.06446227431297302</v>
+        <v>0.05350501835346222</v>
       </c>
       <c r="P19" s="3">
-        <v>0.05424202978610992</v>
+        <v>0.04837219044566154</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.05949036777019501</v>
+        <v>0.06442493945360184</v>
       </c>
       <c r="R19" s="3">
-        <v>0.0752348080277443</v>
+        <v>0.07499434798955917</v>
       </c>
       <c r="S19" s="3">
-        <v>0.05343043431639671</v>
+        <v>0.06771883368492126</v>
       </c>
       <c r="T19" s="3">
-        <v>0.05164673924446106</v>
+        <v>0.0427154079079628</v>
       </c>
       <c r="U19" s="3">
-        <v>0.05417188629508018</v>
+        <v>0.05558116734027863</v>
       </c>
       <c r="V19" s="3">
-        <v>0.05826978757977486</v>
+        <v>0.05439466238021851</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0.04922112450003624</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0.03986551612615585</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0.05415825918316841</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0.04595811292529106</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>0.05003299564123154</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>0.04335599392652512</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>0.05436959490180016</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>0.04689650237560272</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>0.06100371107459068</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>0.07019104063510895</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>0.05953623726963997</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>0.06162036955356598</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>0.05885031446814537</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>0.06276187300682068</v>
+      </c>
+      <c r="AK19" s="3">
+        <v>0.0661989152431488</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3">
-        <v>0.05568352341651917</v>
+        <v>0.04182584211230278</v>
       </c>
       <c r="D20" s="3">
-        <v>0.06294652074575424</v>
+        <v>0.05129294842481613</v>
       </c>
       <c r="E20" s="3">
-        <v>0.06358680874109268</v>
+        <v>0.03480814024806023</v>
       </c>
       <c r="F20" s="3">
-        <v>0.06593162566423416</v>
+        <v>0.05117093771696091</v>
       </c>
       <c r="G20" s="3">
-        <v>0.06259304285049438</v>
+        <v>0.04833404719829559</v>
       </c>
       <c r="H20" s="3">
-        <v>0.05800135433673859</v>
+        <v>0.048069067299366</v>
       </c>
       <c r="I20" s="3">
-        <v>0.05991747230291367</v>
+        <v>0.05557386204600334</v>
       </c>
       <c r="J20" s="3">
-        <v>0.07126646488904953</v>
+        <v>0.06139126420021057</v>
       </c>
       <c r="K20" s="3">
-        <v>0.0711127445101738</v>
+        <v>0.06586334109306335</v>
       </c>
       <c r="L20" s="3">
-        <v>0.06846030056476593</v>
+        <v>0.0534679964184761</v>
       </c>
       <c r="M20" s="3">
-        <v>0.06361842900514603</v>
+        <v>0.06563219428062439</v>
       </c>
       <c r="N20" s="3">
-        <v>0.05840612202882767</v>
+        <v>0.06512010097503662</v>
       </c>
       <c r="O20" s="3">
-        <v>0.07044203579425812</v>
+        <v>0.06314829736948013</v>
       </c>
       <c r="P20" s="3">
-        <v>0.06770632416009903</v>
+        <v>0.05393108725547791</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.06902740150690079</v>
+        <v>0.04710681736469269</v>
       </c>
       <c r="R20" s="3">
-        <v>0.06685420125722885</v>
+        <v>0.07002194970846176</v>
       </c>
       <c r="S20" s="3">
-        <v>0.07106167823076248</v>
+        <v>0.0670926496386528</v>
       </c>
       <c r="T20" s="3">
-        <v>0.0648358091711998</v>
+        <v>0.0396672859787941</v>
       </c>
       <c r="U20" s="3">
-        <v>0.06145447492599487</v>
+        <v>0.04849995672702789</v>
       </c>
       <c r="V20" s="3">
-        <v>0.06356224417686462</v>
+        <v>0.05813154578208923</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0.05196702107787132</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0.03312692046165466</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0.04301448911428452</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0.04275293275713921</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0.04121902957558632</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0.03662437200546265</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0.05722325295209885</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0.04088199883699417</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0.0525919571518898</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0.06424349546432495</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0.05288567766547203</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0.05992143228650093</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0.05846188962459564</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>0.07150141894817352</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0.0650428906083107</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C21" s="3">
-        <v>0.07741671055555344</v>
+        <v>0.03631779924035072</v>
       </c>
       <c r="D21" s="3">
-        <v>0.08465077728033066</v>
+        <v>0.04623919352889061</v>
       </c>
       <c r="E21" s="3">
-        <v>0.08003904670476913</v>
+        <v>0.02831504493951797</v>
       </c>
       <c r="F21" s="3">
-        <v>0.08238181471824646</v>
+        <v>0.04210340231657028</v>
       </c>
       <c r="G21" s="3">
-        <v>0.08591211587190628</v>
+        <v>0.04187864437699318</v>
       </c>
       <c r="H21" s="3">
-        <v>0.04551604017615318</v>
+        <v>0.02718804776668549</v>
       </c>
       <c r="I21" s="3">
-        <v>0.03684009611606598</v>
+        <v>0.04509682208299637</v>
       </c>
       <c r="J21" s="3">
-        <v>0.0643596425652504</v>
+        <v>0.04811655357480049</v>
       </c>
       <c r="K21" s="3">
-        <v>0.0608438216149807</v>
+        <v>0.05275977402925491</v>
       </c>
       <c r="L21" s="3">
-        <v>0.06131934002041817</v>
+        <v>0.05006841942667961</v>
       </c>
       <c r="M21" s="3">
-        <v>0.05129474028944969</v>
+        <v>0.05302145332098007</v>
       </c>
       <c r="N21" s="3">
-        <v>0.04818668961524963</v>
+        <v>0.05028912425041199</v>
       </c>
       <c r="O21" s="3">
-        <v>0.06191098690032959</v>
+        <v>0.03910895064473152</v>
       </c>
       <c r="P21" s="3">
-        <v>0.05681122094392776</v>
+        <v>0.04215022176504135</v>
       </c>
       <c r="Q21" s="3">
-        <v>0.0564119890332222</v>
+        <v>0.04578633606433868</v>
       </c>
       <c r="R21" s="3">
-        <v>0.07883172482252121</v>
+        <v>0.06191197037696838</v>
       </c>
       <c r="S21" s="3">
-        <v>0.06141592934727669</v>
+        <v>0.0555943176150322</v>
       </c>
       <c r="T21" s="3">
-        <v>0.05098916217684746</v>
+        <v>0.03995136171579361</v>
       </c>
       <c r="U21" s="3">
-        <v>0.05919951200485229</v>
+        <v>0.04765269160270691</v>
       </c>
       <c r="V21" s="3">
-        <v>0.04770088195800781</v>
+        <v>0.04116150736808777</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0.04508370906114578</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0.03810977190732956</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>0.04190775007009506</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0.03964045643806458</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>0.04106418788433075</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>0.04059711098670959</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>0.04785863310098648</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>0.03884421661496162</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>0.0420275554060936</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>0.05492454022169113</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>0.04138381779193878</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>0.04908008128404617</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>0.04154990985989571</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>0.05145825445652008</v>
+      </c>
+      <c r="AK21" s="3">
+        <v>0.05379031598567963</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C22" s="3">
-        <v>0.05527074635028839</v>
+        <v>0.04345996677875519</v>
       </c>
       <c r="D22" s="3">
-        <v>0.06340384483337402</v>
+        <v>0.05148835107684135</v>
       </c>
       <c r="E22" s="3">
-        <v>0.05808877944946289</v>
+        <v>0.04212541878223419</v>
       </c>
       <c r="F22" s="3">
-        <v>0.0570618100464344</v>
+        <v>0.05122187733650208</v>
       </c>
       <c r="G22" s="3">
-        <v>0.05977176874876022</v>
+        <v>0.0538061298429966</v>
       </c>
       <c r="H22" s="3">
-        <v>0.04156838729977608</v>
+        <v>0.0380093902349472</v>
       </c>
       <c r="I22" s="3">
-        <v>0.04835209995508194</v>
+        <v>0.05554069206118584</v>
       </c>
       <c r="J22" s="3">
-        <v>0.05014890059828758</v>
+        <v>0.0384172685444355</v>
       </c>
       <c r="K22" s="3">
-        <v>0.04350985214114189</v>
+        <v>0.04901617020368576</v>
       </c>
       <c r="L22" s="3">
-        <v>0.05086508020758629</v>
+        <v>0.03837418556213379</v>
       </c>
       <c r="M22" s="3">
-        <v>0.0380231998860836</v>
+        <v>0.04660826176404953</v>
       </c>
       <c r="N22" s="3">
-        <v>0.04444767534732819</v>
+        <v>0.05338806286454201</v>
       </c>
       <c r="O22" s="3">
-        <v>0.04418804123997688</v>
+        <v>0.04343867301940918</v>
       </c>
       <c r="P22" s="3">
-        <v>0.04088729247450829</v>
+        <v>0.05347929522395134</v>
       </c>
       <c r="Q22" s="3">
-        <v>0.04411395639181137</v>
+        <v>0.03590726479887962</v>
       </c>
       <c r="R22" s="3">
-        <v>0.05748127028346062</v>
+        <v>0.05324629694223404</v>
       </c>
       <c r="S22" s="3">
-        <v>0.04834423586726189</v>
+        <v>0.04888414219021797</v>
       </c>
       <c r="T22" s="3">
-        <v>0.04172942787408829</v>
+        <v>0.02596295066177845</v>
       </c>
       <c r="U22" s="3">
-        <v>0.04687964916229248</v>
+        <v>0.03493905067443848</v>
       </c>
       <c r="V22" s="3">
-        <v>0.05161513015627861</v>
+        <v>0.03577984869480133</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0.03485313802957535</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0.03476716578006744</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0.02841243892908096</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0.02628572285175323</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0.0274377129971981</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0.03013994358479977</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0.04059629514813423</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0.02851015701889992</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0.04201199114322662</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0.05584058910608292</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0.04492136090993881</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0.04489072039723396</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0.05035781860351562</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0.05401359498500824</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0.0512872077524662</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C23" s="3">
-        <v>0.03593956306576729</v>
+        <v>0.04053168371319771</v>
       </c>
       <c r="D23" s="3">
-        <v>0.0434851162135601</v>
+        <v>0.04241828247904778</v>
       </c>
       <c r="E23" s="3">
-        <v>0.04119629040360451</v>
+        <v>0.02727178856730461</v>
       </c>
       <c r="F23" s="3">
-        <v>0.0461449921131134</v>
+        <v>0.04296817630529404</v>
       </c>
       <c r="G23" s="3">
-        <v>0.04105909913778305</v>
+        <v>0.04845541715621948</v>
       </c>
       <c r="H23" s="3">
-        <v>0.03122712671756744</v>
+        <v>0.04076819494366646</v>
       </c>
       <c r="I23" s="3">
-        <v>0.02724014036357403</v>
+        <v>0.04676639661192894</v>
       </c>
       <c r="J23" s="3">
-        <v>0.03561471402645111</v>
+        <v>0.04796464368700981</v>
       </c>
       <c r="K23" s="3">
-        <v>0.03864600136876106</v>
+        <v>0.04516656324267387</v>
       </c>
       <c r="L23" s="3">
-        <v>0.03820298612117767</v>
+        <v>0.02993115782737732</v>
       </c>
       <c r="M23" s="3">
-        <v>0.03438351303339005</v>
+        <v>0.04272709786891937</v>
       </c>
       <c r="N23" s="3">
-        <v>0.03954122960567474</v>
+        <v>0.0451711006462574</v>
       </c>
       <c r="O23" s="3">
-        <v>0.04262750223278999</v>
+        <v>0.04555270075798035</v>
       </c>
       <c r="P23" s="3">
-        <v>0.04369504377245903</v>
+        <v>0.04353577643632889</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.04263526946306229</v>
+        <v>0.03750768303871155</v>
       </c>
       <c r="R23" s="3">
-        <v>0.0446418821811676</v>
+        <v>0.04725352674722672</v>
       </c>
       <c r="S23" s="3">
-        <v>0.03826306760311127</v>
+        <v>0.04963152855634689</v>
       </c>
       <c r="T23" s="3">
-        <v>0.04095486551523209</v>
+        <v>0.01931055448949337</v>
       </c>
       <c r="U23" s="3">
-        <v>0.04579651355743408</v>
+        <v>0.02558374032378197</v>
       </c>
       <c r="V23" s="3">
-        <v>0.04958454146981239</v>
+        <v>0.03904971107840538</v>
+      </c>
+      <c r="W23" s="3">
+        <v>0.02864241600036621</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0.02728731371462345</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>0.02409184537827969</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0.03437415510416031</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>0.02630552649497986</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>0.02897338941693306</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>0.04286137223243713</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>0.02791531570255756</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>0.03853621333837509</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>0.04983876273036003</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>0.03898884356021881</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>0.04271477460861206</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>0.03960749134421349</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>0.050240408629179</v>
+      </c>
+      <c r="AK23" s="3">
+        <v>0.05025966092944145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C24" s="3">
-        <v>0.04285083338618279</v>
+        <v>0.04459739476442337</v>
       </c>
       <c r="D24" s="3">
-        <v>0.04750461503863335</v>
+        <v>0.04378563538193703</v>
       </c>
       <c r="E24" s="3">
-        <v>0.0504801943898201</v>
+        <v>0.0318506695330143</v>
       </c>
       <c r="F24" s="3">
-        <v>0.04819624498486519</v>
+        <v>0.0419265441596508</v>
       </c>
       <c r="G24" s="3">
-        <v>0.05466390773653984</v>
+        <v>0.04389197751879692</v>
       </c>
       <c r="H24" s="3">
-        <v>0.03623387962579727</v>
+        <v>0.03708121925592422</v>
       </c>
       <c r="I24" s="3">
-        <v>0.0252127218991518</v>
+        <v>0.04604129493236542</v>
       </c>
       <c r="J24" s="3">
-        <v>0.04215016216039658</v>
+        <v>0.05750737339258194</v>
       </c>
       <c r="K24" s="3">
-        <v>0.04457505792379379</v>
+        <v>0.05893484503030777</v>
       </c>
       <c r="L24" s="3">
-        <v>0.04409132897853851</v>
+        <v>0.042286217212677</v>
       </c>
       <c r="M24" s="3">
-        <v>0.04195950552821159</v>
+        <v>0.0530998483300209</v>
       </c>
       <c r="N24" s="3">
-        <v>0.03843051567673683</v>
+        <v>0.04969087243080139</v>
       </c>
       <c r="O24" s="3">
-        <v>0.04949138686060905</v>
+        <v>0.04848170280456543</v>
       </c>
       <c r="P24" s="3">
-        <v>0.04423744976520538</v>
+        <v>0.03936135023832321</v>
       </c>
       <c r="Q24" s="3">
-        <v>0.0437854677438736</v>
+        <v>0.06311158835887909</v>
       </c>
       <c r="R24" s="3">
-        <v>0.05556831136345863</v>
+        <v>0.0654127448797226</v>
       </c>
       <c r="S24" s="3">
-        <v>0.04198653623461723</v>
+        <v>0.05416369810700417</v>
       </c>
       <c r="T24" s="3">
-        <v>0.04003307223320007</v>
+        <v>0.03436443954706192</v>
       </c>
       <c r="U24" s="3">
-        <v>0.04597650095820427</v>
+        <v>0.03416559845209122</v>
       </c>
       <c r="V24" s="3">
-        <v>0.04908082261681557</v>
+        <v>0.0433700755238533</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0.03914368525147438</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0.04882124066352844</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0.05865541100502014</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0.0382077544927597</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0.04221696779131889</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0.03824236243963242</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0.04975061863660812</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0.03943581506609917</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0.05137383192777634</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0.06267253309488297</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0.04798229038715363</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0.05575758963823318</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0.04856100678443909</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>0.05516282096505165</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>0.05917451530694962</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C25" s="3">
-        <v>0.05086477845907211</v>
+        <v>0.02717485837638378</v>
       </c>
       <c r="D25" s="3">
-        <v>0.05827320367097855</v>
+        <v>0.03713786974549294</v>
       </c>
       <c r="E25" s="3">
-        <v>0.05547056719660759</v>
+        <v>0.02779367566108704</v>
       </c>
       <c r="F25" s="3">
-        <v>0.05343639850616455</v>
+        <v>0.03585713729262352</v>
       </c>
       <c r="G25" s="3">
-        <v>0.05450224876403809</v>
+        <v>0.03259856998920441</v>
       </c>
       <c r="H25" s="3">
-        <v>0.05510332062840462</v>
+        <v>0.02759663388133049</v>
       </c>
       <c r="I25" s="3">
-        <v>0.04800169914960861</v>
+        <v>0.03836669772863388</v>
       </c>
       <c r="J25" s="3">
-        <v>0.0612727478146553</v>
+        <v>0.04315462708473206</v>
       </c>
       <c r="K25" s="3">
-        <v>0.06302426755428314</v>
+        <v>0.04877632111310959</v>
       </c>
       <c r="L25" s="3">
-        <v>0.06497379392385483</v>
+        <v>0.04270809143781662</v>
       </c>
       <c r="M25" s="3">
-        <v>0.06089957058429718</v>
+        <v>0.04619232937693596</v>
       </c>
       <c r="N25" s="3">
-        <v>0.06063668057322502</v>
+        <v>0.0492013543844223</v>
       </c>
       <c r="O25" s="3">
-        <v>0.06443329155445099</v>
+        <v>0.04689832776784897</v>
       </c>
       <c r="P25" s="3">
-        <v>0.06200312823057175</v>
+        <v>0.04524292051792145</v>
       </c>
       <c r="Q25" s="3">
-        <v>0.06887058168649673</v>
+        <v>0.04102690517902374</v>
       </c>
       <c r="R25" s="3">
-        <v>0.05682945996522903</v>
+        <v>0.05139769241213799</v>
       </c>
       <c r="S25" s="3">
-        <v>0.06180264055728912</v>
+        <v>0.05058661848306656</v>
       </c>
       <c r="T25" s="3">
-        <v>0.06301726400852203</v>
+        <v>0.03014349937438965</v>
       </c>
       <c r="U25" s="3">
-        <v>0.0619967021048069</v>
+        <v>0.03189894556999207</v>
       </c>
       <c r="V25" s="3">
-        <v>0.06788225471973419</v>
+        <v>0.04361437261104584</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0.03693254292011261</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0.02901987545192242</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0.03678077459335327</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0.04038910940289497</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0.03998827934265137</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0.03341063857078552</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0.04929812625050545</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0.0401889979839325</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0.04918580874800682</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0.05390721186995506</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0.04726537317037582</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0.05175751820206642</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0.0476643480360508</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0.0520559586584568</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0.05718675255775452</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C26" s="3">
-        <v>0.06190889701247215</v>
+        <v>0.04363981261849403</v>
       </c>
       <c r="D26" s="3">
-        <v>0.07031510770320892</v>
+        <v>0.0312340222299099</v>
       </c>
       <c r="E26" s="3">
-        <v>0.06157661229372025</v>
+        <v>0.01821250095963478</v>
       </c>
       <c r="F26" s="3">
-        <v>0.06079602986574173</v>
+        <v>0.02472520619630814</v>
       </c>
       <c r="G26" s="3">
-        <v>0.06678753346204758</v>
+        <v>0.03059751912951469</v>
       </c>
       <c r="H26" s="3">
-        <v>0.06004307419061661</v>
+        <v>0.02990028262138367</v>
       </c>
       <c r="I26" s="3">
-        <v>0.04530763626098633</v>
+        <v>0.03298770636320114</v>
       </c>
       <c r="J26" s="3">
-        <v>0.05203212052583694</v>
+        <v>0.0474993996322155</v>
       </c>
       <c r="K26" s="3">
-        <v>0.05766170099377632</v>
+        <v>0.04981315135955811</v>
       </c>
       <c r="L26" s="3">
-        <v>0.05372783169150352</v>
+        <v>0.03986135125160217</v>
       </c>
       <c r="M26" s="3">
-        <v>0.06248462945222855</v>
+        <v>0.04497029632329941</v>
       </c>
       <c r="N26" s="3">
-        <v>0.0628986731171608</v>
+        <v>0.0441880002617836</v>
       </c>
       <c r="O26" s="3">
-        <v>0.05620377883315086</v>
+        <v>0.05112447217106819</v>
       </c>
       <c r="P26" s="3">
-        <v>0.05165714770555496</v>
+        <v>0.04231320321559906</v>
       </c>
       <c r="Q26" s="3">
-        <v>0.05370797961950302</v>
+        <v>0.03911170363426208</v>
       </c>
       <c r="R26" s="3">
-        <v>0.06445474922657013</v>
+        <v>0.05485352873802185</v>
       </c>
       <c r="S26" s="3">
-        <v>0.0537770614027977</v>
+        <v>0.05598742887377739</v>
       </c>
       <c r="T26" s="3">
-        <v>0.05565264821052551</v>
+        <v>0.03142647445201874</v>
       </c>
       <c r="U26" s="3">
-        <v>0.05681662261486053</v>
+        <v>0.03459616005420685</v>
       </c>
       <c r="V26" s="3">
-        <v>0.04482579231262207</v>
+        <v>0.04585812985897064</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0.039349764585495</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0.01906409673392773</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0.02515705488622189</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0.02466084063053131</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>0.0239320807158947</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>0.01547265239059925</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>0.043585404753685</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>0.02604198269546032</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>0.03475931286811829</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>0.04928404465317726</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>0.03708125650882721</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>0.04219098016619682</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>0.03130783140659332</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>0.05035736411809921</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>0.04661008715629578</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C27" s="3">
-        <v>0.05550887435674667</v>
+        <v>0.03030634857714176</v>
       </c>
       <c r="D27" s="3">
-        <v>0.05618337169289589</v>
+        <v>0.05784234032034874</v>
       </c>
       <c r="E27" s="3">
-        <v>0.06037354469299316</v>
+        <v>0.04309983551502228</v>
       </c>
       <c r="F27" s="3">
-        <v>0.0567755252122879</v>
+        <v>0.0547323115170002</v>
       </c>
       <c r="G27" s="3">
-        <v>0.0585925281047821</v>
+        <v>0.05403648316860199</v>
       </c>
       <c r="H27" s="3">
-        <v>0.05119961872696877</v>
+        <v>0.04306432977318764</v>
       </c>
       <c r="I27" s="3">
-        <v>0.04742181673645973</v>
+        <v>0.06051134690642357</v>
       </c>
       <c r="J27" s="3">
-        <v>0.06151574850082397</v>
+        <v>0.04465806111693382</v>
       </c>
       <c r="K27" s="3">
-        <v>0.05777045339345932</v>
+        <v>0.06172066926956177</v>
       </c>
       <c r="L27" s="3">
-        <v>0.06076027825474739</v>
+        <v>0.05206814408302307</v>
       </c>
       <c r="M27" s="3">
-        <v>0.05608770623803139</v>
+        <v>0.0615219809114933</v>
       </c>
       <c r="N27" s="3">
-        <v>0.04860430583357811</v>
+        <v>0.06351610273122787</v>
       </c>
       <c r="O27" s="3">
-        <v>0.06547853350639343</v>
+        <v>0.05259901657700539</v>
       </c>
       <c r="P27" s="3">
-        <v>0.06002994626760483</v>
+        <v>0.06350290030241013</v>
       </c>
       <c r="Q27" s="3">
-        <v>0.06257690489292145</v>
+        <v>0.036660335958004</v>
       </c>
       <c r="R27" s="3">
-        <v>0.06120708957314491</v>
+        <v>0.0568644292652607</v>
       </c>
       <c r="S27" s="3">
-        <v>0.06149968132376671</v>
+        <v>0.04879895970225334</v>
       </c>
       <c r="T27" s="3">
-        <v>0.05679577961564064</v>
+        <v>0.03989234194159508</v>
       </c>
       <c r="U27" s="3">
-        <v>0.05628659576177597</v>
+        <v>0.04592785611748695</v>
       </c>
       <c r="V27" s="3">
-        <v>0.05998899042606354</v>
+        <v>0.04762202501296997</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0.04766561836004257</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0.01993451826274395</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>0.03382853046059608</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0.03413137793540955</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>0.0392419695854187</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>0.03171807155013084</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>0.05257328599691391</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>0.03944233059883118</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>0.03805532306432724</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>0.05097812414169312</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>0.03929426148533821</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>0.04562825337052345</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>0.04851388558745384</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>0.05266161262989044</v>
+      </c>
+      <c r="AK27" s="3">
+        <v>0.0514739602804184</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C28" s="3">
-        <v>0.07052730768918991</v>
+        <v>0.05837695300579071</v>
       </c>
       <c r="D28" s="3">
-        <v>0.08234023302793503</v>
+        <v>0.0496869683265686</v>
       </c>
       <c r="E28" s="3">
-        <v>0.0840824544429779</v>
+        <v>0.03815951943397522</v>
       </c>
       <c r="F28" s="3">
-        <v>0.0870315358042717</v>
+        <v>0.04889130964875221</v>
       </c>
       <c r="G28" s="3">
-        <v>0.0815097987651825</v>
+        <v>0.0489027127623558</v>
       </c>
       <c r="H28" s="3">
-        <v>0.05163615942001343</v>
+        <v>0.03973734006285667</v>
       </c>
       <c r="I28" s="3">
-        <v>0.04775033891201019</v>
+        <v>0.05417002737522125</v>
       </c>
       <c r="J28" s="3">
-        <v>0.0676715150475502</v>
+        <v>0.06013848632574081</v>
       </c>
       <c r="K28" s="3">
-        <v>0.07141873240470886</v>
+        <v>0.05473466590046883</v>
       </c>
       <c r="L28" s="3">
-        <v>0.0678277239203453</v>
+        <v>0.04794948175549507</v>
       </c>
       <c r="M28" s="3">
-        <v>0.03756236284971237</v>
+        <v>0.05303369089961052</v>
       </c>
       <c r="N28" s="3">
-        <v>0.03523396700620651</v>
+        <v>0.055585578083992</v>
       </c>
       <c r="O28" s="3">
-        <v>0.04560297727584839</v>
+        <v>0.04734691604971886</v>
       </c>
       <c r="P28" s="3">
-        <v>0.03859782218933105</v>
+        <v>0.05090618878602982</v>
       </c>
       <c r="Q28" s="3">
-        <v>0.0477646067738533</v>
+        <v>0.0364270992577076</v>
       </c>
       <c r="R28" s="3">
-        <v>0.08801998198032379</v>
+        <v>0.05390643700957298</v>
       </c>
       <c r="S28" s="3">
-        <v>0.0695849061012268</v>
+        <v>0.03906009718775749</v>
       </c>
       <c r="T28" s="3">
-        <v>0.04712551459670067</v>
+        <v>0.02681353874504566</v>
       </c>
       <c r="U28" s="3">
-        <v>0.07127310335636139</v>
+        <v>0.03163164481520653</v>
       </c>
       <c r="V28" s="3">
-        <v>0.06121814623475075</v>
+        <v>0.03714461624622345</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0.04236729070544243</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0.06935007125139236</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0.04273966699838638</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0.03063821047544479</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0.04353195428848267</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0.03709382191300392</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0.04844270646572113</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0.03995499387383461</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0.04920157790184021</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0.05555124580860138</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0.04847853630781174</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0.05251745879650116</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0.05005314573645592</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0.05838481336832047</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0.05806002020835876</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C29" s="3">
-        <v>0.02309689484536648</v>
+        <v>0.0137880127876997</v>
       </c>
       <c r="D29" s="3">
-        <v>0.04500937089323997</v>
+        <v>0.02872065454721451</v>
       </c>
       <c r="E29" s="3">
-        <v>0.02958342432975769</v>
+        <v>0.009618690237402916</v>
       </c>
       <c r="F29" s="3">
-        <v>0.03689376264810562</v>
+        <v>0.02523002773523331</v>
       </c>
       <c r="G29" s="3">
-        <v>0.03445021435618401</v>
+        <v>0.02899043634533882</v>
       </c>
       <c r="H29" s="3">
-        <v>0.008366022258996964</v>
+        <v>0.01856187917292118</v>
       </c>
       <c r="I29" s="3">
-        <v>0.01315937750041485</v>
+        <v>0.03042514063417912</v>
       </c>
       <c r="J29" s="3">
-        <v>0.02040413953363895</v>
+        <v>0.03710708022117615</v>
       </c>
       <c r="K29" s="3">
-        <v>0.01940578781068325</v>
+        <v>0.03779922053217888</v>
       </c>
       <c r="L29" s="3">
-        <v>0.01941830478608608</v>
+        <v>0.02628271281719208</v>
       </c>
       <c r="M29" s="3">
-        <v>0.01706176437437534</v>
+        <v>0.03744304180145264</v>
       </c>
       <c r="N29" s="3">
-        <v>0.02465206198394299</v>
+        <v>0.04077081009745598</v>
       </c>
       <c r="O29" s="3">
-        <v>0.02434305660426617</v>
+        <v>0.03771620616316795</v>
       </c>
       <c r="P29" s="3">
-        <v>0.02053791284561157</v>
+        <v>0.02930782735347748</v>
       </c>
       <c r="Q29" s="3">
-        <v>0.02516209334135056</v>
+        <v>0.02978071756660938</v>
       </c>
       <c r="R29" s="3">
-        <v>0.02920463308691978</v>
+        <v>0.0343632772564888</v>
       </c>
       <c r="S29" s="3">
-        <v>0.01882277987897396</v>
+        <v>0.04042129963636398</v>
       </c>
       <c r="T29" s="3">
-        <v>0.02262003347277641</v>
+        <v>0.01837282627820969</v>
       </c>
       <c r="U29" s="3">
-        <v>0.02217671275138855</v>
+        <v>0.02956273034214973</v>
       </c>
       <c r="V29" s="3">
-        <v>0.02007493562996387</v>
+        <v>0.03394059091806412</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0.0244866069406271</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0.03314166516065598</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0.02787459455430508</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0.01923039369285107</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0.02356279827654362</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0.02640576846897602</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0.04158323258161545</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0.0240548811852932</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0.03728718310594559</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0.02974623814225197</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0.01926524378359318</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0.02856324799358845</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0.03160056099295616</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0.03039581142365932</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0.03403832390904427</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C30" s="3">
-        <v>0.06344722956418991</v>
+        <v>0.0412844754755497</v>
       </c>
       <c r="D30" s="3">
-        <v>0.06623969972133636</v>
+        <v>0.06299374997615814</v>
       </c>
       <c r="E30" s="3">
-        <v>0.06818125396966934</v>
+        <v>0.0508991964161396</v>
       </c>
       <c r="F30" s="3">
-        <v>0.06553395837545395</v>
+        <v>0.06267750263214111</v>
       </c>
       <c r="G30" s="3">
-        <v>0.07091349363327026</v>
+        <v>0.06523168087005615</v>
       </c>
       <c r="H30" s="3">
-        <v>0.04713615030050278</v>
+        <v>0.05335019156336784</v>
       </c>
       <c r="I30" s="3">
-        <v>0.05713290721178055</v>
+        <v>0.06548447906970978</v>
       </c>
       <c r="J30" s="3">
-        <v>0.06285711377859116</v>
+        <v>0.05355941504240036</v>
       </c>
       <c r="K30" s="3">
-        <v>0.06126857548952103</v>
+        <v>0.06787135452032089</v>
       </c>
       <c r="L30" s="3">
-        <v>0.06140226125717163</v>
+        <v>0.05698511749505997</v>
       </c>
       <c r="M30" s="3">
-        <v>0.05774875730276108</v>
+        <v>0.06624455749988556</v>
       </c>
       <c r="N30" s="3">
-        <v>0.06100490689277649</v>
+        <v>0.06810498982667923</v>
       </c>
       <c r="O30" s="3">
-        <v>0.0663808137178421</v>
+        <v>0.05930603668093681</v>
       </c>
       <c r="P30" s="3">
-        <v>0.06306688487529755</v>
+        <v>0.05640405043959618</v>
       </c>
       <c r="Q30" s="3">
-        <v>0.06694324314594269</v>
+        <v>0.03576815128326416</v>
       </c>
       <c r="R30" s="3">
-        <v>0.07043788582086563</v>
+        <v>0.06997695565223694</v>
       </c>
       <c r="S30" s="3">
-        <v>0.06346210092306137</v>
+        <v>0.06847167760133743</v>
       </c>
       <c r="T30" s="3">
-        <v>0.06062008440494537</v>
+        <v>0.04487833753228188</v>
       </c>
       <c r="U30" s="3">
-        <v>0.06575612723827362</v>
+        <v>0.05410273745656013</v>
       </c>
       <c r="V30" s="3">
-        <v>0.06131423637270927</v>
+        <v>0.05894209071993828</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0.05233011394739151</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0.03750250488519669</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0.054151251912117</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0.04719660058617592</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0.05040980130434036</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0.05354124680161476</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0.06131117790937424</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0.04897198081016541</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0.04672538861632347</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0.06242049112915993</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0.05409164354205132</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0.05675570666790009</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0.05295920744538307</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0.06442082673311234</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0.06283212453126907</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C31" s="3">
-        <v>0.06224064156413078</v>
+        <v>0.04411015287041664</v>
       </c>
       <c r="D31" s="3">
-        <v>0.06791872531175613</v>
+        <v>0.0430111475288868</v>
       </c>
       <c r="E31" s="3">
-        <v>0.06720218062400818</v>
+        <v>0.02692326344549656</v>
       </c>
       <c r="F31" s="3">
-        <v>0.0659913644194603</v>
+        <v>0.04118108749389648</v>
       </c>
       <c r="G31" s="3">
-        <v>0.07358606159687042</v>
+        <v>0.04496131092309952</v>
       </c>
       <c r="H31" s="3">
-        <v>0.03387067094445229</v>
+        <v>0.03043665178120136</v>
       </c>
       <c r="I31" s="3">
-        <v>0.03654878586530685</v>
+        <v>0.04564908146858215</v>
       </c>
       <c r="J31" s="3">
-        <v>0.04534222930669785</v>
+        <v>0.05580909550189972</v>
       </c>
       <c r="K31" s="3">
-        <v>0.04150504991412163</v>
+        <v>0.04387195408344269</v>
       </c>
       <c r="L31" s="3">
-        <v>0.04360433295369148</v>
+        <v>0.04618822410702705</v>
       </c>
       <c r="M31" s="3">
-        <v>0.04143340140581131</v>
+        <v>0.04373278468847275</v>
       </c>
       <c r="N31" s="3">
-        <v>0.03123845718801022</v>
+        <v>0.04543593525886536</v>
       </c>
       <c r="O31" s="3">
-        <v>0.04697922989726067</v>
+        <v>0.03522995486855507</v>
       </c>
       <c r="P31" s="3">
-        <v>0.04063888639211655</v>
+        <v>0.0346265435218811</v>
       </c>
       <c r="Q31" s="3">
-        <v>0.04763880744576454</v>
+        <v>0.04940635338425636</v>
       </c>
       <c r="R31" s="3">
-        <v>0.06718109548091888</v>
+        <v>0.05163037776947021</v>
       </c>
       <c r="S31" s="3">
-        <v>0.04656733945012093</v>
+        <v>0.05318624526262283</v>
       </c>
       <c r="T31" s="3">
-        <v>0.04518062993884087</v>
+        <v>0.02985764667391777</v>
       </c>
       <c r="U31" s="3">
-        <v>0.04315857961773872</v>
+        <v>0.02979648858308792</v>
       </c>
       <c r="V31" s="3">
-        <v>0.04641880467534065</v>
+        <v>0.03467947244644165</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0.04093985632061958</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0.03449663519859314</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0.02277487330138683</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0.03487224131822586</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0.03015323728322983</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0.02129844948649406</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0.0337303951382637</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0.029408885166049</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0.04551095515489578</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0.04818429425358772</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0.04215461015701294</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0.04451264441013336</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0.04946276545524597</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0.0488610565662384</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0.05099036544561386</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C32" s="3">
-        <v>0.06504296511411667</v>
+        <v>0.03130257874727249</v>
       </c>
       <c r="D32" s="3">
-        <v>0.08202583342790604</v>
+        <v>0.04890353977680206</v>
       </c>
       <c r="E32" s="3">
-        <v>0.06644979864358902</v>
+        <v>0.03747215494513512</v>
       </c>
       <c r="F32" s="3">
-        <v>0.07701481133699417</v>
+        <v>0.05241740867495537</v>
       </c>
       <c r="G32" s="3">
-        <v>0.06996507197618484</v>
+        <v>0.05407475307583809</v>
       </c>
       <c r="H32" s="3">
-        <v>0.04505139589309692</v>
+        <v>0.03697499260306358</v>
       </c>
       <c r="I32" s="3">
-        <v>0.03254881128668785</v>
+        <v>0.05396777763962746</v>
       </c>
       <c r="J32" s="3">
-        <v>0.06082535535097122</v>
+        <v>0.05182681605219841</v>
       </c>
       <c r="K32" s="3">
-        <v>0.05648525059223175</v>
+        <v>0.04828726500272751</v>
       </c>
       <c r="L32" s="3">
-        <v>0.05487474799156189</v>
+        <v>0.03653734922409058</v>
       </c>
       <c r="M32" s="3">
-        <v>0.0687670186161995</v>
+        <v>0.04845568910241127</v>
       </c>
       <c r="N32" s="3">
-        <v>0.05923439562320709</v>
+        <v>0.05538490787148476</v>
       </c>
       <c r="O32" s="3">
-        <v>0.0804816260933876</v>
+        <v>0.03209571167826653</v>
       </c>
       <c r="P32" s="3">
-        <v>0.07664753496646881</v>
+        <v>0.0479312352836132</v>
       </c>
       <c r="Q32" s="3">
-        <v>0.07016272842884064</v>
+        <v>0.0377013273537159</v>
       </c>
       <c r="R32" s="3">
-        <v>0.071316197514534</v>
+        <v>0.05426891148090363</v>
       </c>
       <c r="S32" s="3">
-        <v>0.0528937354683876</v>
+        <v>0.05478504300117493</v>
       </c>
       <c r="T32" s="3">
-        <v>0.06382270902395248</v>
+        <v>0.0299205593764782</v>
       </c>
       <c r="U32" s="3">
-        <v>0.03867862373590469</v>
+        <v>0.04427838325500488</v>
       </c>
       <c r="V32" s="3">
-        <v>0.05567989870905876</v>
+        <v>0.03524729982018471</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0.03919737413525581</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0.01109005510807037</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0.01251282915472984</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0.01957372389733791</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0.02411158941686153</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0.02563928440213203</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0.03942381963133812</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0.02218989282846451</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0.04240187257528305</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0.05440755560994148</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0.0467381477355957</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0.05083030089735985</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0.06877891719341278</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0.05024760216474533</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>0.05685348808765411</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C33" s="3">
-        <v>0.04076596349477768</v>
+        <v>0.02560997195541859</v>
       </c>
       <c r="D33" s="3">
-        <v>0.05142776668071747</v>
+        <v>0.04359165206551552</v>
       </c>
       <c r="E33" s="3">
-        <v>0.05333864688873291</v>
+        <v>0.03054250404238701</v>
       </c>
       <c r="F33" s="3">
-        <v>0.05544079095125198</v>
+        <v>0.0429251454770565</v>
       </c>
       <c r="G33" s="3">
-        <v>0.05442412197589874</v>
+        <v>0.04418320581316948</v>
       </c>
       <c r="H33" s="3">
-        <v>0.01535324566066265</v>
+        <v>0.03993764519691467</v>
       </c>
       <c r="I33" s="3">
-        <v>0.009284982457756996</v>
+        <v>0.04643275588750839</v>
       </c>
       <c r="J33" s="3">
-        <v>0.0336802713572979</v>
+        <v>0.03425240889191628</v>
       </c>
       <c r="K33" s="3">
-        <v>0.03015064261853695</v>
+        <v>0.04300764203071594</v>
       </c>
       <c r="L33" s="3">
-        <v>0.03265850618481636</v>
+        <v>0.03631701692938805</v>
       </c>
       <c r="M33" s="3">
-        <v>0.0261884517967701</v>
+        <v>0.04036514461040497</v>
       </c>
       <c r="N33" s="3">
-        <v>0.02192018181085587</v>
+        <v>0.04323457926511765</v>
       </c>
       <c r="O33" s="3">
-        <v>0.04030654206871986</v>
+        <v>0.03799021616578102</v>
       </c>
       <c r="P33" s="3">
-        <v>0.03660499304533005</v>
+        <v>0.03095364011824131</v>
       </c>
       <c r="Q33" s="3">
-        <v>0.04005718231201172</v>
+        <v>0.02483269199728966</v>
       </c>
       <c r="R33" s="3">
-        <v>0.05449935048818588</v>
+        <v>0.04999853670597076</v>
       </c>
       <c r="S33" s="3">
-        <v>0.03480081260204315</v>
+        <v>0.05472658574581146</v>
       </c>
       <c r="T33" s="3">
-        <v>0.03045844100415707</v>
+        <v>0.02235562726855278</v>
       </c>
       <c r="U33" s="3">
-        <v>0.03635251894593239</v>
+        <v>0.03027826733887196</v>
       </c>
       <c r="V33" s="3">
-        <v>0.03583009168505669</v>
+        <v>0.03760950267314911</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0.031856469810009</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0.01964378543198109</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>0.03598390147089958</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0.03110379353165627</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>0.03214684128761292</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>0.02902800962328911</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>0.04164492711424828</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>0.03073333390057087</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>0.03706203028559685</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>0.04835611954331398</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0.03561544790863991</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>0.03973198682069778</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>0.03847481682896614</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>0.04408840462565422</v>
+      </c>
+      <c r="AK33" s="3">
+        <v>0.04925690963864326</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C34" s="3">
-        <v>0.07443996518850327</v>
+        <v>0.05413768440485001</v>
       </c>
       <c r="D34" s="3">
-        <v>0.07492808997631073</v>
+        <v>0.05202242359519005</v>
       </c>
       <c r="E34" s="3">
-        <v>0.07633868604898453</v>
+        <v>0.04516938701272011</v>
       </c>
       <c r="F34" s="3">
-        <v>0.0761808305978775</v>
+        <v>0.05042535066604614</v>
       </c>
       <c r="G34" s="3">
-        <v>0.07871665805578232</v>
+        <v>0.05038395896553993</v>
       </c>
       <c r="H34" s="3">
-        <v>0.05440869182348251</v>
+        <v>0.05025669932365417</v>
       </c>
       <c r="I34" s="3">
-        <v>0.0368046946823597</v>
+        <v>0.05495474860072136</v>
       </c>
       <c r="J34" s="3">
-        <v>0.06233541294932365</v>
+        <v>0.06225426122546196</v>
       </c>
       <c r="K34" s="3">
-        <v>0.05802801251411438</v>
+        <v>0.06379804760217667</v>
       </c>
       <c r="L34" s="3">
-        <v>0.06197674572467804</v>
+        <v>0.05991164967417717</v>
       </c>
       <c r="M34" s="3">
-        <v>0.06037430465221405</v>
+        <v>0.05835168808698654</v>
       </c>
       <c r="N34" s="3">
-        <v>0.04753776267170906</v>
+        <v>0.06259219348430634</v>
       </c>
       <c r="O34" s="3">
-        <v>0.06629678606987</v>
+        <v>0.05911215022206306</v>
       </c>
       <c r="P34" s="3">
-        <v>0.06181993708014488</v>
+        <v>0.04293379932641983</v>
       </c>
       <c r="Q34" s="3">
-        <v>0.0676301047205925</v>
+        <v>0.06473289430141449</v>
       </c>
       <c r="R34" s="3">
-        <v>0.08040289580821991</v>
+        <v>0.0692058801651001</v>
       </c>
       <c r="S34" s="3">
-        <v>0.06373128294944763</v>
+        <v>0.06623589247465134</v>
       </c>
       <c r="T34" s="3">
-        <v>0.06234639137983322</v>
+        <v>0.04353161156177521</v>
       </c>
       <c r="U34" s="3">
-        <v>0.06593659520149231</v>
+        <v>0.04513425752520561</v>
       </c>
       <c r="V34" s="3">
-        <v>0.06994874030351639</v>
+        <v>0.05648856982588768</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0.05050981789827347</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0.05463852360844612</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0.04413698613643646</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0.04862229898571968</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0.04699805751442909</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0.04385725408792496</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0.05714339762926102</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0.04717483371496201</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0.06589439511299133</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0.06175210699439049</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0.05842611566185951</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0.0580800399184227</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0.06352563947439194</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0.06638780981302261</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0.06654264777898788</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C35" s="3">
-        <v>0.03367352485656738</v>
+        <v>0.01810723729431629</v>
       </c>
       <c r="D35" s="3">
-        <v>0.03970513492822647</v>
+        <v>0.03327999636530876</v>
       </c>
       <c r="E35" s="3">
-        <v>0.04207142069935799</v>
+        <v>0.03073501773178577</v>
       </c>
       <c r="F35" s="3">
-        <v>0.04512806236743927</v>
+        <v>0.02836636640131474</v>
       </c>
       <c r="G35" s="3">
-        <v>0.03413582220673561</v>
+        <v>0.03586943820118904</v>
       </c>
       <c r="H35" s="3">
-        <v>0.03128752112388611</v>
+        <v>0.02379526570439339</v>
       </c>
       <c r="I35" s="3">
-        <v>-0.002090937225148082</v>
+        <v>0.0360531285405159</v>
       </c>
       <c r="J35" s="3">
-        <v>0.03788687288761139</v>
+        <v>0.02286473661661148</v>
       </c>
       <c r="K35" s="3">
-        <v>0.03441886976361275</v>
+        <v>0.0388837456703186</v>
       </c>
       <c r="L35" s="3">
-        <v>0.03871232271194458</v>
+        <v>0.03373393416404724</v>
       </c>
       <c r="M35" s="3">
-        <v>0.03412441164255142</v>
+        <v>0.03245455026626587</v>
       </c>
       <c r="N35" s="3">
-        <v>0.01863485015928745</v>
+        <v>0.03581631183624268</v>
       </c>
       <c r="O35" s="3">
-        <v>0.04196184128522873</v>
+        <v>0.03156981244683266</v>
       </c>
       <c r="P35" s="3">
-        <v>0.03362135589122772</v>
+        <v>0.03454839065670967</v>
       </c>
       <c r="Q35" s="3">
-        <v>0.04353662952780724</v>
+        <v>0.01748028770089149</v>
       </c>
       <c r="R35" s="3">
-        <v>0.0451582707464695</v>
+        <v>0.04151251912117004</v>
       </c>
       <c r="S35" s="3">
-        <v>0.04068073630332947</v>
+        <v>0.05270346626639366</v>
       </c>
       <c r="T35" s="3">
-        <v>0.03271343559026718</v>
+        <v>0.01571277529001236</v>
       </c>
       <c r="U35" s="3">
-        <v>0.0502491407096386</v>
+        <v>0.02213493548333645</v>
       </c>
       <c r="V35" s="3">
-        <v>0.0503927618265152</v>
+        <v>0.02608159184455872</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0.02596668899059296</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0.000007622875273227692</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>0.02297318354249001</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0.03690028563141823</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>0.02839037030935287</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>0.02145879529416561</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>0.03278420865535736</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>0.03021393716335297</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>0.03114412911236286</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>0.04560944437980652</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0.03607329726219177</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>0.04158191010355949</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>0.04751290380954742</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>0.04044048115611076</v>
+      </c>
+      <c r="AK35" s="3">
+        <v>0.04980217665433884</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C36" s="3">
-        <v>0.0445607416331768</v>
+        <v>0.02287409640848637</v>
       </c>
       <c r="D36" s="3">
-        <v>0.05169693380594254</v>
+        <v>0.01806777715682983</v>
       </c>
       <c r="E36" s="3">
-        <v>0.03868784382939339</v>
+        <v>0.002580780535936356</v>
       </c>
       <c r="F36" s="3">
-        <v>0.04153517633676529</v>
+        <v>0.0146244028583169</v>
       </c>
       <c r="G36" s="3">
-        <v>0.04097702354192734</v>
+        <v>0.01135711744427681</v>
       </c>
       <c r="H36" s="3">
-        <v>0.04080038517713547</v>
+        <v>0.01373195089399815</v>
       </c>
       <c r="I36" s="3">
-        <v>0.03614872694015503</v>
+        <v>0.01562192849814892</v>
       </c>
       <c r="J36" s="3">
-        <v>0.04003040492534637</v>
+        <v>0.04413092508912086</v>
       </c>
       <c r="K36" s="3">
-        <v>0.04432237520813942</v>
+        <v>0.03948356211185455</v>
       </c>
       <c r="L36" s="3">
-        <v>0.04540669918060303</v>
+        <v>0.02832916565239429</v>
       </c>
       <c r="M36" s="3">
-        <v>0.03549332171678543</v>
+        <v>0.03576722741127014</v>
       </c>
       <c r="N36" s="3">
-        <v>0.04447838664054871</v>
+        <v>0.03293638676404953</v>
       </c>
       <c r="O36" s="3">
-        <v>0.0391232930123806</v>
+        <v>0.0351572073996067</v>
       </c>
       <c r="P36" s="3">
-        <v>0.04002983495593071</v>
+        <v>0.02662228047847748</v>
       </c>
       <c r="Q36" s="3">
-        <v>0.04199014976620674</v>
+        <v>0.02974526025354862</v>
       </c>
       <c r="R36" s="3">
-        <v>0.04165849089622498</v>
+        <v>0.04351123049855232</v>
       </c>
       <c r="S36" s="3">
-        <v>0.03913029283285141</v>
+        <v>0.03918828442692757</v>
       </c>
       <c r="T36" s="3">
-        <v>0.03734564781188965</v>
+        <v>0.02637100405991077</v>
       </c>
       <c r="U36" s="3">
-        <v>0.03940948098897934</v>
+        <v>0.02944377064704895</v>
       </c>
       <c r="V36" s="3">
-        <v>0.02910007163882256</v>
+        <v>0.03261294588446617</v>
+      </c>
+      <c r="W36" s="3">
+        <v>0.02951286919414997</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0.02076413482427597</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>0.0165506936609745</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>0.02598954737186432</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>0.02374828234314919</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>0.02421484887599945</v>
+      </c>
+      <c r="AC36" s="3">
+        <v>0.04494253173470497</v>
+      </c>
+      <c r="AD36" s="3">
+        <v>0.02559279277920723</v>
+      </c>
+      <c r="AE36" s="3">
+        <v>0.02298946492373943</v>
+      </c>
+      <c r="AF36" s="3">
+        <v>0.04054490476846695</v>
+      </c>
+      <c r="AG36" s="3">
+        <v>0.02460994571447372</v>
+      </c>
+      <c r="AH36" s="3">
+        <v>0.0317307636141777</v>
+      </c>
+      <c r="AI36" s="3">
+        <v>0.02617895789444447</v>
+      </c>
+      <c r="AJ36" s="3">
+        <v>0.03820803016424179</v>
+      </c>
+      <c r="AK36" s="3">
+        <v>0.03445734456181526</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C37" s="3">
-        <v>0.1018679663538933</v>
+        <v>0.08284971863031387</v>
       </c>
       <c r="D37" s="3">
-        <v>0.1059979274868965</v>
+        <v>0.06181828305125237</v>
       </c>
       <c r="E37" s="3">
-        <v>0.09784972667694092</v>
+        <v>0.04201066866517067</v>
       </c>
       <c r="F37" s="3">
-        <v>0.1013874113559723</v>
+        <v>0.05866217985749245</v>
       </c>
       <c r="G37" s="3">
-        <v>0.107510469853878</v>
+        <v>0.05976679921150208</v>
       </c>
       <c r="H37" s="3">
-        <v>0.0715193897485733</v>
+        <v>0.0580645464360714</v>
       </c>
       <c r="I37" s="3">
-        <v>0.05806522443890572</v>
+        <v>0.06638269871473312</v>
       </c>
       <c r="J37" s="3">
-        <v>0.07939360290765762</v>
+        <v>0.07007627189159393</v>
       </c>
       <c r="K37" s="3">
-        <v>0.07860114425420761</v>
+        <v>0.07043413072824478</v>
       </c>
       <c r="L37" s="3">
-        <v>0.08258131146430969</v>
+        <v>0.05750231817364693</v>
       </c>
       <c r="M37" s="3">
-        <v>0.0673692598938942</v>
+        <v>0.0693570077419281</v>
       </c>
       <c r="N37" s="3">
-        <v>0.06086070835590363</v>
+        <v>0.06433413922786713</v>
       </c>
       <c r="O37" s="3">
-        <v>0.07345209270715714</v>
+        <v>0.06264351308345795</v>
       </c>
       <c r="P37" s="3">
-        <v>0.06172023713588715</v>
+        <v>0.04890099167823792</v>
       </c>
       <c r="Q37" s="3">
-        <v>0.07301095128059387</v>
+        <v>0.05035794526338577</v>
       </c>
       <c r="R37" s="3">
-        <v>0.1015879139304161</v>
+        <v>0.06738930940628052</v>
       </c>
       <c r="S37" s="3">
-        <v>0.0793861374258995</v>
+        <v>0.06007754802703857</v>
       </c>
       <c r="T37" s="3">
-        <v>0.07288271933794022</v>
+        <v>0.03326369822025299</v>
       </c>
       <c r="U37" s="3">
-        <v>0.07133538275957108</v>
+        <v>0.04583163559436798</v>
       </c>
       <c r="V37" s="3">
-        <v>0.06985059380531311</v>
+        <v>0.04116848111152649</v>
+      </c>
+      <c r="W37" s="3">
+        <v>0.04084982350468636</v>
+      </c>
+      <c r="X37" s="3">
+        <v>0.04949368163943291</v>
+      </c>
+      <c r="Y37" s="3">
+        <v>0.03569015115499496</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>0.03860639035701752</v>
+      </c>
+      <c r="AA37" s="3">
+        <v>0.04317250475287437</v>
+      </c>
+      <c r="AB37" s="3">
+        <v>0.04270245879888535</v>
+      </c>
+      <c r="AC37" s="3">
+        <v>0.0524907186627388</v>
+      </c>
+      <c r="AD37" s="3">
+        <v>0.03967051208019257</v>
+      </c>
+      <c r="AE37" s="3">
+        <v>0.04878025129437447</v>
+      </c>
+      <c r="AF37" s="3">
+        <v>0.0661669597029686</v>
+      </c>
+      <c r="AG37" s="3">
+        <v>0.05042339116334915</v>
+      </c>
+      <c r="AH37" s="3">
+        <v>0.05941328778862953</v>
+      </c>
+      <c r="AI37" s="3">
+        <v>0.05018887668848038</v>
+      </c>
+      <c r="AJ37" s="3">
+        <v>0.06510938704013824</v>
+      </c>
+      <c r="AK37" s="3">
+        <v>0.06704381108283997</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C38" s="3">
-        <v>0.03598418086767197</v>
+        <v>0.01833749562501907</v>
       </c>
       <c r="D38" s="3">
-        <v>0.03390705585479736</v>
+        <v>0.01821556687355042</v>
       </c>
       <c r="E38" s="3">
-        <v>0.03327865153551102</v>
+        <v>0.009312029927968979</v>
       </c>
       <c r="F38" s="3">
-        <v>0.03592710942029953</v>
+        <v>0.01736349985003471</v>
       </c>
       <c r="G38" s="3">
-        <v>0.02990369684994221</v>
+        <v>0.01233661733567715</v>
       </c>
       <c r="H38" s="3">
-        <v>0.04785255715250969</v>
+        <v>0.02747494354844093</v>
       </c>
       <c r="I38" s="3">
-        <v>0.04253029823303223</v>
+        <v>0.02145183645188808</v>
       </c>
       <c r="J38" s="3">
-        <v>0.04429890215396881</v>
+        <v>0.02894218266010284</v>
       </c>
       <c r="K38" s="3">
-        <v>0.05151072889566422</v>
+        <v>0.04496266320347786</v>
       </c>
       <c r="L38" s="3">
-        <v>0.0482594408094883</v>
+        <v>0.03344779461622238</v>
       </c>
       <c r="M38" s="3">
-        <v>0.04238763451576233</v>
+        <v>0.04200939834117889</v>
       </c>
       <c r="N38" s="3">
-        <v>0.03988201916217804</v>
+        <v>0.04001861065626144</v>
       </c>
       <c r="O38" s="3">
-        <v>0.04447478428483009</v>
+        <v>0.05006597191095352</v>
       </c>
       <c r="P38" s="3">
-        <v>0.04132538288831711</v>
+        <v>0.03164471685886383</v>
       </c>
       <c r="Q38" s="3">
-        <v>0.04203354567289352</v>
+        <v>0.0250288974493742</v>
       </c>
       <c r="R38" s="3">
-        <v>0.04098152369260788</v>
+        <v>0.03153488785028458</v>
       </c>
       <c r="S38" s="3">
-        <v>0.04573161900043488</v>
+        <v>0.03384364768862724</v>
       </c>
       <c r="T38" s="3">
-        <v>0.04276608675718307</v>
+        <v>0.01828001439571381</v>
       </c>
       <c r="U38" s="3">
-        <v>0.0497182235121727</v>
+        <v>0.02617073990404606</v>
       </c>
       <c r="V38" s="3">
-        <v>0.03946313261985779</v>
+        <v>0.04005088657140732</v>
+      </c>
+      <c r="W38" s="3">
+        <v>0.02784102037549019</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0.02662941627204418</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>0.02201587706804276</v>
+      </c>
+      <c r="Z38" s="3">
+        <v>0.02624515071511269</v>
+      </c>
+      <c r="AA38" s="3">
+        <v>0.02760254591703415</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>0.02965567260980606</v>
+      </c>
+      <c r="AC38" s="3">
+        <v>0.04769053310155869</v>
+      </c>
+      <c r="AD38" s="3">
+        <v>0.02862265333533287</v>
+      </c>
+      <c r="AE38" s="3">
+        <v>0.02577026002109051</v>
+      </c>
+      <c r="AF38" s="3">
+        <v>0.0335199274122715</v>
+      </c>
+      <c r="AG38" s="3">
+        <v>0.02816022932529449</v>
+      </c>
+      <c r="AH38" s="3">
+        <v>0.03491843491792679</v>
+      </c>
+      <c r="AI38" s="3">
+        <v>0.03309442102909088</v>
+      </c>
+      <c r="AJ38" s="3">
+        <v>0.03715850040316582</v>
+      </c>
+      <c r="AK38" s="3">
+        <v>0.03789403662085533</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C39" s="3">
-        <v>0.04620067402720451</v>
+        <v>0.06604287028312683</v>
       </c>
       <c r="D39" s="3">
-        <v>0.05537459254264832</v>
+        <v>0.03843825310468674</v>
       </c>
       <c r="E39" s="3">
-        <v>0.05007727816700935</v>
+        <v>0.03361907228827477</v>
       </c>
       <c r="F39" s="3">
-        <v>0.05116851627826691</v>
+        <v>0.03959662094712257</v>
       </c>
       <c r="G39" s="3">
-        <v>0.05543209984898567</v>
+        <v>0.03758861124515533</v>
       </c>
       <c r="H39" s="3">
-        <v>0.04889778792858124</v>
+        <v>0.02882540784776211</v>
       </c>
       <c r="I39" s="3">
-        <v>0.0603889599442482</v>
+        <v>0.04050937667489052</v>
       </c>
       <c r="J39" s="3">
-        <v>0.0654793456196785</v>
+        <v>0.06544175744056702</v>
       </c>
       <c r="K39" s="3">
-        <v>0.0637534037232399</v>
+        <v>0.06284943968057632</v>
       </c>
       <c r="L39" s="3">
-        <v>0.0650303065776825</v>
+        <v>0.04818151518702507</v>
       </c>
       <c r="M39" s="3">
-        <v>0.05845742672681808</v>
+        <v>0.05435341969132423</v>
       </c>
       <c r="N39" s="3">
-        <v>0.07340405881404877</v>
+        <v>0.05810413882136345</v>
       </c>
       <c r="O39" s="3">
-        <v>0.06373243778944016</v>
+        <v>0.05546728149056435</v>
       </c>
       <c r="P39" s="3">
-        <v>0.05713482946157455</v>
+        <v>0.041135523468256</v>
       </c>
       <c r="Q39" s="3">
-        <v>0.06825793534517288</v>
+        <v>0.04580807313323021</v>
       </c>
       <c r="R39" s="3">
-        <v>0.04849419742822647</v>
+        <v>0.06567096710205078</v>
       </c>
       <c r="S39" s="3">
-        <v>0.06524024158716202</v>
+        <v>0.06517248600721359</v>
       </c>
       <c r="T39" s="3">
-        <v>0.06326741725206375</v>
+        <v>0.04080764949321747</v>
       </c>
       <c r="U39" s="3">
-        <v>0.05844099447131157</v>
+        <v>0.04956177622079849</v>
       </c>
       <c r="V39" s="3">
-        <v>0.06105873733758926</v>
+        <v>0.05132674053311348</v>
+      </c>
+      <c r="W39" s="3">
+        <v>0.04816577583551407</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0.03725966811180115</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>0.03746778890490532</v>
+      </c>
+      <c r="Z39" s="3">
+        <v>0.03909681364893913</v>
+      </c>
+      <c r="AA39" s="3">
+        <v>0.04178642854094505</v>
+      </c>
+      <c r="AB39" s="3">
+        <v>0.04088126495480537</v>
+      </c>
+      <c r="AC39" s="3">
+        <v>0.06180552020668983</v>
+      </c>
+      <c r="AD39" s="3">
+        <v>0.04068982601165771</v>
+      </c>
+      <c r="AE39" s="3">
+        <v>0.04951853677630424</v>
+      </c>
+      <c r="AF39" s="3">
+        <v>0.06413894891738892</v>
+      </c>
+      <c r="AG39" s="3">
+        <v>0.04401420801877975</v>
+      </c>
+      <c r="AH39" s="3">
+        <v>0.05161955580115318</v>
+      </c>
+      <c r="AI39" s="3">
+        <v>0.05076699703931808</v>
+      </c>
+      <c r="AJ39" s="3">
+        <v>0.05430348217487335</v>
+      </c>
+      <c r="AK39" s="3">
+        <v>0.05802246555685997</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C40" s="3">
-        <v>0.06773538142442703</v>
+        <v>0.06524708122015</v>
       </c>
       <c r="D40" s="3">
-        <v>0.07469026744365692</v>
+        <v>0.0672873929142952</v>
       </c>
       <c r="E40" s="3">
-        <v>0.07527483254671097</v>
+        <v>0.0527554415166378</v>
       </c>
       <c r="F40" s="3">
-        <v>0.07551563531160355</v>
+        <v>0.06766786426305771</v>
       </c>
       <c r="G40" s="3">
-        <v>0.08047523349523544</v>
+        <v>0.06627295166254044</v>
       </c>
       <c r="H40" s="3">
-        <v>0.05356424301862717</v>
+        <v>0.06883946806192398</v>
       </c>
       <c r="I40" s="3">
-        <v>0.07535966485738754</v>
+        <v>0.07098487764596939</v>
       </c>
       <c r="J40" s="3">
-        <v>0.0643211305141449</v>
+        <v>0.07483275979757309</v>
       </c>
       <c r="K40" s="3">
-        <v>0.06745120137929916</v>
+        <v>0.0796750858426094</v>
       </c>
       <c r="L40" s="3">
-        <v>0.0646405890583992</v>
+        <v>0.06666279584169388</v>
       </c>
       <c r="M40" s="3">
-        <v>0.04762290418148041</v>
+        <v>0.07797369360923767</v>
       </c>
       <c r="N40" s="3">
-        <v>0.0645739808678627</v>
+        <v>0.07646993547677994</v>
       </c>
       <c r="O40" s="3">
-        <v>0.0590166300535202</v>
+        <v>0.07611224055290222</v>
       </c>
       <c r="P40" s="3">
-        <v>0.05777991563081741</v>
+        <v>0.06957881897687912</v>
       </c>
       <c r="Q40" s="3">
-        <v>0.06034061312675476</v>
+        <v>0.06724799424409866</v>
       </c>
       <c r="R40" s="3">
-        <v>0.07602118700742722</v>
+        <v>0.07489059120416641</v>
       </c>
       <c r="S40" s="3">
-        <v>0.06325522065162659</v>
+        <v>0.06890156120061874</v>
       </c>
       <c r="T40" s="3">
-        <v>0.05274227261543274</v>
+        <v>0.05062795802950859</v>
       </c>
       <c r="U40" s="3">
-        <v>0.06703999638557434</v>
+        <v>0.05637654662132263</v>
       </c>
       <c r="V40" s="3">
-        <v>0.06734407693147659</v>
+        <v>0.06707463413476944</v>
+      </c>
+      <c r="W40" s="3">
+        <v>0.06075754761695862</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0.05877607688307762</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>0.06749214231967926</v>
+      </c>
+      <c r="Z40" s="3">
+        <v>0.06288815289735794</v>
+      </c>
+      <c r="AA40" s="3">
+        <v>0.06343293935060501</v>
+      </c>
+      <c r="AB40" s="3">
+        <v>0.06015412509441376</v>
+      </c>
+      <c r="AC40" s="3">
+        <v>0.07956544309854507</v>
+      </c>
+      <c r="AD40" s="3">
+        <v>0.06399483978748322</v>
+      </c>
+      <c r="AE40" s="3">
+        <v>0.05880710110068321</v>
+      </c>
+      <c r="AF40" s="3">
+        <v>0.0661187469959259</v>
+      </c>
+      <c r="AG40" s="3">
+        <v>0.06127497926354408</v>
+      </c>
+      <c r="AH40" s="3">
+        <v>0.06351207941770554</v>
+      </c>
+      <c r="AI40" s="3">
+        <v>0.05971739813685417</v>
+      </c>
+      <c r="AJ40" s="3">
+        <v>0.07176078855991364</v>
+      </c>
+      <c r="AK40" s="3">
+        <v>0.06932400912046432</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C41" s="3">
-        <v>0.03040705062448978</v>
+        <v>0.02724659442901611</v>
       </c>
       <c r="D41" s="3">
-        <v>0.03775272518396378</v>
+        <v>0.04433620721101761</v>
       </c>
       <c r="E41" s="3">
-        <v>0.04126189276576042</v>
+        <v>0.04514581337571144</v>
       </c>
       <c r="F41" s="3">
-        <v>0.03845052793622017</v>
+        <v>0.04443380236625671</v>
       </c>
       <c r="G41" s="3">
-        <v>0.0381295457482338</v>
+        <v>0.05597299337387085</v>
       </c>
       <c r="H41" s="3">
-        <v>0.03532018139958382</v>
+        <v>0.04210420697927475</v>
       </c>
       <c r="I41" s="3">
-        <v>0.03160426020622253</v>
+        <v>0.04929612204432487</v>
       </c>
       <c r="J41" s="3">
-        <v>0.0410974882543087</v>
+        <v>0.0483141653239727</v>
       </c>
       <c r="K41" s="3">
-        <v>0.03554488345980644</v>
+        <v>0.05621693283319473</v>
       </c>
       <c r="L41" s="3">
-        <v>0.03932405263185501</v>
+        <v>0.06155167892575264</v>
       </c>
       <c r="M41" s="3">
-        <v>0.03379210829734802</v>
+        <v>0.05857313424348831</v>
       </c>
       <c r="N41" s="3">
-        <v>0.02879555150866508</v>
+        <v>0.0614449679851532</v>
       </c>
       <c r="O41" s="3">
-        <v>0.04228616878390312</v>
+        <v>0.04734601080417633</v>
       </c>
       <c r="P41" s="3">
-        <v>0.02804373949766159</v>
+        <v>0.04730201885104179</v>
       </c>
       <c r="Q41" s="3">
-        <v>0.0371721163392067</v>
+        <v>0.04295208305120468</v>
       </c>
       <c r="R41" s="3">
-        <v>0.04116378352046013</v>
+        <v>0.04966698959469795</v>
       </c>
       <c r="S41" s="3">
-        <v>0.03816478699445724</v>
+        <v>0.04993511363863945</v>
       </c>
       <c r="T41" s="3">
-        <v>0.03008241951465607</v>
+        <v>0.0307196918874979</v>
       </c>
       <c r="U41" s="3">
-        <v>0.04143539443612099</v>
+        <v>0.03741912543773651</v>
       </c>
       <c r="V41" s="3">
-        <v>0.02587859146296978</v>
+        <v>0.03749094530940056</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0.03400501981377602</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0.0142510998994112</v>
+      </c>
+      <c r="Y41" s="3">
+        <v>0.02921251766383648</v>
+      </c>
+      <c r="Z41" s="3">
+        <v>0.03556313738226891</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>0.03922505304217339</v>
+      </c>
+      <c r="AB41" s="3">
+        <v>0.04292699322104454</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>0.04437235742807388</v>
+      </c>
+      <c r="AD41" s="3">
+        <v>0.03891360759735107</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>0.03429533168673515</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>0.05002585798501968</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0.03545684739947319</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0.0449184887111187</v>
+      </c>
+      <c r="AI41" s="3">
+        <v>0.03925195708870888</v>
+      </c>
+      <c r="AJ41" s="3">
+        <v>0.04375743493437767</v>
+      </c>
+      <c r="AK41" s="3">
+        <v>0.05377675592899323</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3">
-        <v>0.09771264344453812</v>
+        <v>0.06420081853866577</v>
       </c>
       <c r="D42" s="3">
-        <v>0.1116870492696762</v>
+        <v>0.0775357186794281</v>
       </c>
       <c r="E42" s="3">
-        <v>0.09705311805009842</v>
+        <v>0.06073769927024841</v>
       </c>
       <c r="F42" s="3">
-        <v>0.0980910211801529</v>
+        <v>0.07444558292627335</v>
       </c>
       <c r="G42" s="3">
-        <v>0.1051329076290131</v>
+        <v>0.07649075239896774</v>
       </c>
       <c r="H42" s="3">
-        <v>0.06174932792782784</v>
+        <v>0.06738816201686859</v>
       </c>
       <c r="I42" s="3">
-        <v>0.08910714089870453</v>
+        <v>0.07942590117454529</v>
       </c>
       <c r="J42" s="3">
-        <v>0.07308600842952728</v>
+        <v>0.07973913848400116</v>
       </c>
       <c r="K42" s="3">
-        <v>0.07697369903326035</v>
+        <v>0.07857471704483032</v>
       </c>
       <c r="L42" s="3">
-        <v>0.07270525395870209</v>
+        <v>0.07249083369970322</v>
       </c>
       <c r="M42" s="3">
-        <v>0.06536763906478882</v>
+        <v>0.07731931656599045</v>
       </c>
       <c r="N42" s="3">
-        <v>0.0854652151465416</v>
+        <v>0.0781523659825325</v>
       </c>
       <c r="O42" s="3">
-        <v>0.08227252960205078</v>
+        <v>0.070147804915905</v>
       </c>
       <c r="P42" s="3">
-        <v>0.0790698304772377</v>
+        <v>0.06839960813522339</v>
       </c>
       <c r="Q42" s="3">
-        <v>0.07570787519216537</v>
+        <v>0.07914498448371887</v>
       </c>
       <c r="R42" s="3">
-        <v>0.09310586005449295</v>
+        <v>0.08959275484085083</v>
       </c>
       <c r="S42" s="3">
-        <v>0.06999684870243073</v>
+        <v>0.08118993043899536</v>
       </c>
       <c r="T42" s="3">
-        <v>0.07448585331439972</v>
+        <v>0.07047376036643982</v>
       </c>
       <c r="U42" s="3">
-        <v>0.06887752562761307</v>
+        <v>0.0798419937491417</v>
       </c>
       <c r="V42" s="3">
-        <v>0.06811320781707764</v>
+        <v>0.07800742238759995</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0.07975487411022186</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0.04740672931075096</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0.06654834747314453</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0.05673108249902725</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0.06044716387987137</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0.05697232857346535</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0.0717618390917778</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0.05963249132037163</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0.06850641965866089</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0.07757434993982315</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0.07211406528949738</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0.07666602730751038</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0.07168297469615936</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0.08499304205179214</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0.08003738522529602</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C43" s="3">
-        <v>0.03474771976470947</v>
+        <v>0.003273573704063892</v>
       </c>
       <c r="D43" s="3">
-        <v>0.03322266787290573</v>
+        <v>0.01501655858010054</v>
       </c>
       <c r="E43" s="3">
-        <v>0.03363916277885437</v>
+        <v>0.004996177740395069</v>
       </c>
       <c r="F43" s="3">
-        <v>0.02746047824621201</v>
+        <v>0.01082847733050585</v>
       </c>
       <c r="G43" s="3">
-        <v>0.02920723892748356</v>
+        <v>0.006002405192703009</v>
       </c>
       <c r="H43" s="3">
-        <v>0.04265058785676956</v>
+        <v>0.001426160335540771</v>
       </c>
       <c r="I43" s="3">
-        <v>0.01756908558309078</v>
+        <v>0.01489037647843361</v>
       </c>
       <c r="J43" s="3">
-        <v>0.03029519878327847</v>
+        <v>0.02302901446819305</v>
       </c>
       <c r="K43" s="3">
-        <v>0.03312936797738075</v>
+        <v>0.0429733470082283</v>
       </c>
       <c r="L43" s="3">
-        <v>0.03752260655164719</v>
+        <v>0.03659906983375549</v>
       </c>
       <c r="M43" s="3">
-        <v>0.03879499435424805</v>
+        <v>0.03820974007248878</v>
       </c>
       <c r="N43" s="3">
-        <v>0.02996287308633327</v>
+        <v>0.0228616539388895</v>
       </c>
       <c r="O43" s="3">
-        <v>0.0313061848282814</v>
+        <v>0.03267846629023552</v>
       </c>
       <c r="P43" s="3">
-        <v>0.0281048733741045</v>
+        <v>0.02976246923208237</v>
       </c>
       <c r="Q43" s="3">
-        <v>0.03098594583570957</v>
+        <v>0.0166474599391222</v>
       </c>
       <c r="R43" s="3">
-        <v>0.0387321263551712</v>
+        <v>0.03730981796979904</v>
       </c>
       <c r="S43" s="3">
-        <v>0.03172726184129715</v>
+        <v>0.02936622314155102</v>
       </c>
       <c r="T43" s="3">
-        <v>0.03081101924180984</v>
+        <v>-0.004453293979167938</v>
       </c>
       <c r="U43" s="3">
-        <v>0.04006831720471382</v>
+        <v>-0.003555384464561939</v>
       </c>
       <c r="V43" s="3">
-        <v>0.03002695180475712</v>
+        <v>0.008959556929767132</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0.004833689890801907</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0.02986663207411766</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0.02502736449241638</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0.01984789967536926</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0.01526706572622061</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>-0.003576131537556648</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0.02511176280677319</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0.01562044396996498</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>0.02379833720624447</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0.03621039167046547</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0.02032674849033356</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0.02841388061642647</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0.006657833233475685</v>
+      </c>
+      <c r="AJ43" s="3">
+        <v>0.02818083949387074</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>0.03417829424142838</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C44" s="3">
-        <v>0.0115935979411006</v>
+        <v>0.01669619046151638</v>
       </c>
       <c r="D44" s="3">
-        <v>0.01893415115773678</v>
+        <v>0.008527432568371296</v>
       </c>
       <c r="E44" s="3">
-        <v>0.02112420089542866</v>
+        <v>-0.008130938746035099</v>
       </c>
       <c r="F44" s="3">
-        <v>0.02130595222115517</v>
+        <v>0.008338000625371933</v>
       </c>
       <c r="G44" s="3">
-        <v>0.02314626798033714</v>
+        <v>0.004168072715401649</v>
       </c>
       <c r="H44" s="3">
-        <v>0.01983807049691677</v>
+        <v>0.003882022574543953</v>
       </c>
       <c r="I44" s="3">
-        <v>0.004466659389436245</v>
+        <v>0.01338273473083973</v>
       </c>
       <c r="J44" s="3">
-        <v>0.0157715305685997</v>
+        <v>0.01991016045212746</v>
       </c>
       <c r="K44" s="3">
-        <v>0.01722562871873379</v>
+        <v>0.0251079834997654</v>
       </c>
       <c r="L44" s="3">
-        <v>0.01673968695104122</v>
+        <v>0.01032099593430758</v>
       </c>
       <c r="M44" s="3">
-        <v>0.01678695343434811</v>
+        <v>0.01721419021487236</v>
       </c>
       <c r="N44" s="3">
-        <v>0.01625247672200203</v>
+        <v>0.01892567612230778</v>
       </c>
       <c r="O44" s="3">
-        <v>0.0203300453722477</v>
+        <v>0.01829284057021141</v>
       </c>
       <c r="P44" s="3">
-        <v>0.01849702373147011</v>
+        <v>0.01201958023011684</v>
       </c>
       <c r="Q44" s="3">
-        <v>0.01459266431629658</v>
+        <v>0.02274052798748016</v>
       </c>
       <c r="R44" s="3">
-        <v>0.02390458434820175</v>
+        <v>0.01938769407570362</v>
       </c>
       <c r="S44" s="3">
-        <v>0.01514348480850458</v>
+        <v>0.015947625041008</v>
       </c>
       <c r="T44" s="3">
-        <v>0.01230782456696033</v>
+        <v>-0.001648963312618434</v>
       </c>
       <c r="U44" s="3">
-        <v>0.01318280771374702</v>
+        <v>-0.003967640921473503</v>
       </c>
       <c r="V44" s="3">
-        <v>0.008058587089180946</v>
+        <v>0.01428777817636728</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0.008286064490675926</v>
+      </c>
+      <c r="X44" s="3">
+        <v>-0.005948393605649471</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>-0.01070161070674658</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0.0005372394807636738</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>-0.009910267777740955</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>-0.02228344976902008</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0.011802788823843</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>-0.007586062420159578</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0.01585772633552551</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0.0181694645434618</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0.009217921644449234</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0.01480723824352026</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0.009630202315747738</v>
+      </c>
+      <c r="AJ44" s="3">
+        <v>0.02254860103130341</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0.01818792708218098</v>
       </c>
     </row>
   </sheetData>
